--- a/output/pdf_financials_xlsx/FUN.P.xlsx
+++ b/output/pdf_financials_xlsx/FUN.P.xlsx
@@ -1329,10 +1329,10 @@
         </is>
       </c>
       <c r="C34" s="3" t="n">
-        <v>0</v>
+        <v>0.399712</v>
       </c>
       <c r="D34" s="3" t="n">
-        <v>0</v>
+        <v>0.351412</v>
       </c>
       <c r="E34" s="1" t="inlineStr">
         <is>
@@ -1385,10 +1385,10 @@
         </is>
       </c>
       <c r="C36" s="3" t="n">
-        <v>0</v>
+        <v>0.399712</v>
       </c>
       <c r="D36" s="3" t="n">
-        <v>0</v>
+        <v>0.351412</v>
       </c>
       <c r="E36" s="1" t="inlineStr">
         <is>
@@ -4059,7 +4059,7 @@
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>Cash</t>
+          <t>CashAndCashEquivalents</t>
         </is>
       </c>
       <c r="E2" t="inlineStr">

--- a/output/pdf_financials_xlsx/FUN.P.xlsx
+++ b/output/pdf_financials_xlsx/FUN.P.xlsx
@@ -1323,16 +1323,14 @@
           <t xml:space="preserve">    Cash and Cash Equivalents</t>
         </is>
       </c>
-      <c r="B34" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="B34" s="3" t="n">
+        <v>0.213227</v>
       </c>
       <c r="C34" s="3" t="n">
-        <v>0.399712</v>
+        <v>0.351412</v>
       </c>
       <c r="D34" s="3" t="n">
-        <v>0.351412</v>
+        <v>0.320547</v>
       </c>
       <c r="E34" s="1" t="inlineStr">
         <is>
@@ -1351,10 +1349,8 @@
           <t xml:space="preserve">    Marketable Securities</t>
         </is>
       </c>
-      <c r="B35" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="B35" s="3" t="n">
+        <v>0</v>
       </c>
       <c r="C35" s="3" t="n">
         <v>0</v>
@@ -1379,16 +1375,14 @@
           <t xml:space="preserve">  Cash, Cash Equivalents, Marketable Securities</t>
         </is>
       </c>
-      <c r="B36" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="B36" s="3" t="n">
+        <v>0.213227</v>
       </c>
       <c r="C36" s="3" t="n">
-        <v>0.399712</v>
+        <v>0.351412</v>
       </c>
       <c r="D36" s="3" t="n">
-        <v>0.351412</v>
+        <v>0.320547</v>
       </c>
       <c r="E36" s="1" t="inlineStr">
         <is>
@@ -1407,10 +1401,8 @@
           <t xml:space="preserve">    Accounts Receivable</t>
         </is>
       </c>
-      <c r="B37" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="B37" s="3" t="n">
+        <v>0</v>
       </c>
       <c r="C37" s="3" t="n">
         <v>0</v>
@@ -1435,10 +1427,8 @@
           <t xml:space="preserve">    Notes Receivable</t>
         </is>
       </c>
-      <c r="B38" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="B38" s="3" t="n">
+        <v>0</v>
       </c>
       <c r="C38" s="3" t="n">
         <v>0</v>
@@ -1463,10 +1453,8 @@
           <t xml:space="preserve">    Loans Receivable</t>
         </is>
       </c>
-      <c r="B39" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="B39" s="3" t="n">
+        <v>0</v>
       </c>
       <c r="C39" s="3" t="n">
         <v>0</v>
@@ -1491,10 +1479,8 @@
           <t xml:space="preserve">    Other Current Receivables</t>
         </is>
       </c>
-      <c r="B40" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="B40" s="3" t="n">
+        <v>0</v>
       </c>
       <c r="C40" s="3" t="n">
         <v>0</v>
@@ -1519,10 +1505,8 @@
           <t xml:space="preserve">  Total Receivables</t>
         </is>
       </c>
-      <c r="B41" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="B41" s="3" t="n">
+        <v>0</v>
       </c>
       <c r="C41" s="3" t="n">
         <v>0</v>
@@ -1547,10 +1531,8 @@
           <t xml:space="preserve">    Inventories, Raw Materials &amp; Components</t>
         </is>
       </c>
-      <c r="B42" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="B42" s="3" t="n">
+        <v>0</v>
       </c>
       <c r="C42" s="3" t="n">
         <v>0</v>
@@ -1575,10 +1557,8 @@
           <t xml:space="preserve">    Inventories, Work In Process</t>
         </is>
       </c>
-      <c r="B43" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="B43" s="3" t="n">
+        <v>0</v>
       </c>
       <c r="C43" s="3" t="n">
         <v>0</v>
@@ -1603,10 +1583,8 @@
           <t xml:space="preserve">    Inventories, Inventories Adjustments</t>
         </is>
       </c>
-      <c r="B44" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="B44" s="3" t="n">
+        <v>0</v>
       </c>
       <c r="C44" s="3" t="n">
         <v>0</v>
@@ -1631,10 +1609,8 @@
           <t xml:space="preserve">    Inventories, Finished Goods</t>
         </is>
       </c>
-      <c r="B45" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="B45" s="3" t="n">
+        <v>0</v>
       </c>
       <c r="C45" s="3" t="n">
         <v>0</v>
@@ -1659,10 +1635,8 @@
           <t xml:space="preserve">    Inventories, Other</t>
         </is>
       </c>
-      <c r="B46" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="B46" s="3" t="n">
+        <v>0</v>
       </c>
       <c r="C46" s="3" t="n">
         <v>0</v>
@@ -1687,10 +1661,8 @@
           <t xml:space="preserve">  Total Inventories</t>
         </is>
       </c>
-      <c r="B47" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="B47" s="3" t="n">
+        <v>0</v>
       </c>
       <c r="C47" s="3" t="n">
         <v>0</v>
@@ -1715,10 +1687,8 @@
           <t xml:space="preserve">  Other Current Assets</t>
         </is>
       </c>
-      <c r="B48" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="B48" s="3" t="n">
+        <v>0</v>
       </c>
       <c r="C48" s="3" t="n">
         <v>0</v>
@@ -1775,10 +1745,8 @@
           <t xml:space="preserve">  Investments And Advances</t>
         </is>
       </c>
-      <c r="B50" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="B50" s="3" t="n">
+        <v>0</v>
       </c>
       <c r="C50" s="3" t="n">
         <v>0</v>
@@ -1803,10 +1771,8 @@
           <t xml:space="preserve">      Land And Improvements</t>
         </is>
       </c>
-      <c r="B51" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="B51" s="3" t="n">
+        <v>0</v>
       </c>
       <c r="C51" s="3" t="n">
         <v>0</v>
@@ -1831,10 +1797,8 @@
           <t xml:space="preserve">      Buildings And Improvements</t>
         </is>
       </c>
-      <c r="B52" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="B52" s="3" t="n">
+        <v>0</v>
       </c>
       <c r="C52" s="3" t="n">
         <v>0</v>
@@ -1859,10 +1823,8 @@
           <t xml:space="preserve">      Machinery, Furniture, Equipment</t>
         </is>
       </c>
-      <c r="B53" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="B53" s="3" t="n">
+        <v>0</v>
       </c>
       <c r="C53" s="3" t="n">
         <v>0</v>
@@ -1887,10 +1849,8 @@
           <t xml:space="preserve">      Construction In Progress</t>
         </is>
       </c>
-      <c r="B54" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="B54" s="3" t="n">
+        <v>0</v>
       </c>
       <c r="C54" s="3" t="n">
         <v>0</v>
@@ -1947,10 +1907,8 @@
           <t xml:space="preserve">    Gross Property, Plant and Equipment</t>
         </is>
       </c>
-      <c r="B56" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="B56" s="3" t="n">
+        <v>0</v>
       </c>
       <c r="C56" s="3" t="n">
         <v>0</v>
@@ -1975,10 +1933,8 @@
           <t xml:space="preserve">    Accumulated Depreciation</t>
         </is>
       </c>
-      <c r="B57" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="B57" s="3" t="n">
+        <v>0</v>
       </c>
       <c r="C57" s="3" t="n">
         <v>0</v>
@@ -2003,10 +1959,8 @@
           <t xml:space="preserve">  Property, Plant and Equipment</t>
         </is>
       </c>
-      <c r="B58" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="B58" s="3" t="n">
+        <v>0</v>
       </c>
       <c r="C58" s="3" t="n">
         <v>0</v>
@@ -2031,10 +1985,8 @@
           <t xml:space="preserve">  Intangible Assets</t>
         </is>
       </c>
-      <c r="B59" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="B59" s="3" t="n">
+        <v>0</v>
       </c>
       <c r="C59" s="3" t="n">
         <v>0</v>
@@ -2059,10 +2011,8 @@
           <t xml:space="preserve">    Goodwill</t>
         </is>
       </c>
-      <c r="B60" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="B60" s="3" t="n">
+        <v>0</v>
       </c>
       <c r="C60" s="3" t="n">
         <v>0</v>
@@ -2087,10 +2037,8 @@
           <t xml:space="preserve">  Other Long Term Assets</t>
         </is>
       </c>
-      <c r="B61" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="B61" s="3" t="n">
+        <v>0</v>
       </c>
       <c r="C61" s="3" t="n">
         <v>0</v>
@@ -2147,16 +2095,14 @@
           <t>Total Assets</t>
         </is>
       </c>
-      <c r="B63" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="B63" s="3" t="n">
+        <v>0.222227</v>
       </c>
       <c r="C63" s="3" t="n">
-        <v>0.399712</v>
+        <v>0.351412</v>
       </c>
       <c r="D63" s="3" t="n">
-        <v>0.351412</v>
+        <v>0.320547</v>
       </c>
       <c r="E63" s="1" t="inlineStr">
         <is>
@@ -2175,10 +2121,8 @@
           <t xml:space="preserve">    Accounts Payable</t>
         </is>
       </c>
-      <c r="B64" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="B64" s="3" t="n">
+        <v>0</v>
       </c>
       <c r="C64" s="3" t="n">
         <v>0</v>
@@ -2203,10 +2147,8 @@
           <t xml:space="preserve">    Total Tax Payable</t>
         </is>
       </c>
-      <c r="B65" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="B65" s="3" t="n">
+        <v>0</v>
       </c>
       <c r="C65" s="3" t="n">
         <v>0</v>
@@ -2231,10 +2173,8 @@
           <t xml:space="preserve">    Other Current Payables</t>
         </is>
       </c>
-      <c r="B66" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="B66" s="3" t="n">
+        <v>0</v>
       </c>
       <c r="C66" s="3" t="n">
         <v>0</v>
@@ -2259,10 +2199,8 @@
           <t xml:space="preserve">    Current Accrued Expense</t>
         </is>
       </c>
-      <c r="B67" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="B67" s="3" t="n">
+        <v>0</v>
       </c>
       <c r="C67" s="3" t="n">
         <v>0</v>
@@ -2287,16 +2225,14 @@
           <t xml:space="preserve">  Accounts Payable &amp; Accrued Expense</t>
         </is>
       </c>
-      <c r="B68" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="B68" s="3" t="n">
+        <v>0.005575</v>
       </c>
       <c r="C68" s="3" t="n">
-        <v>0.011021</v>
+        <v>0.014021</v>
       </c>
       <c r="D68" s="3" t="n">
-        <v>0.014021</v>
+        <v>0.013712</v>
       </c>
       <c r="E68" s="1" t="inlineStr">
         <is>
@@ -2315,10 +2251,8 @@
           <t xml:space="preserve">    Short-Term Debt</t>
         </is>
       </c>
-      <c r="B69" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="B69" s="3" t="n">
+        <v>0</v>
       </c>
       <c r="C69" s="3" t="n">
         <v>0</v>
@@ -2343,10 +2277,8 @@
           <t xml:space="preserve">    Short-Term Capital Lease Obligation</t>
         </is>
       </c>
-      <c r="B70" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="B70" s="3" t="n">
+        <v>0</v>
       </c>
       <c r="C70" s="3" t="n">
         <v>0</v>
@@ -2371,10 +2303,8 @@
           <t xml:space="preserve">  Short-Term Debt &amp; Capital Lease Obligation</t>
         </is>
       </c>
-      <c r="B71" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="B71" s="3" t="n">
+        <v>0</v>
       </c>
       <c r="C71" s="3" t="n">
         <v>0</v>
@@ -2399,10 +2329,8 @@
           <t xml:space="preserve">    Current Deferred Revenue</t>
         </is>
       </c>
-      <c r="B72" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="B72" s="3" t="n">
+        <v>0</v>
       </c>
       <c r="C72" s="3" t="n">
         <v>0</v>
@@ -2427,10 +2355,8 @@
           <t xml:space="preserve">    Current Deferred Taxes Liabilities</t>
         </is>
       </c>
-      <c r="B73" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="B73" s="3" t="n">
+        <v>0</v>
       </c>
       <c r="C73" s="3" t="n">
         <v>0</v>
@@ -2455,10 +2381,8 @@
           <t xml:space="preserve">  Deferred Tax And Revenue</t>
         </is>
       </c>
-      <c r="B74" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="B74" s="3" t="n">
+        <v>0</v>
       </c>
       <c r="C74" s="3" t="n">
         <v>0</v>
@@ -2483,10 +2407,8 @@
           <t xml:space="preserve">  Other Current Liabilities</t>
         </is>
       </c>
-      <c r="B75" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="B75" s="3" t="n">
+        <v>0</v>
       </c>
       <c r="C75" s="3" t="n">
         <v>0</v>
@@ -2543,10 +2465,8 @@
           <t xml:space="preserve">    Long-Term Debt</t>
         </is>
       </c>
-      <c r="B77" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="B77" s="3" t="n">
+        <v>0</v>
       </c>
       <c r="C77" s="3" t="n">
         <v>0</v>
@@ -2571,10 +2491,8 @@
           <t xml:space="preserve">    Long-Term Capital Lease Obligation</t>
         </is>
       </c>
-      <c r="B78" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="B78" s="3" t="n">
+        <v>0</v>
       </c>
       <c r="C78" s="3" t="n">
         <v>0</v>
@@ -2599,10 +2517,8 @@
           <t xml:space="preserve">  Long-Term Debt &amp; Capital Lease Obligation</t>
         </is>
       </c>
-      <c r="B79" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="B79" s="3" t="n">
+        <v>0</v>
       </c>
       <c r="C79" s="3" t="n">
         <v>0</v>
@@ -2659,10 +2575,8 @@
           <t xml:space="preserve">  Pension And Retirement Benefit</t>
         </is>
       </c>
-      <c r="B81" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="B81" s="3" t="n">
+        <v>0</v>
       </c>
       <c r="C81" s="3" t="n">
         <v>0</v>
@@ -2687,10 +2601,8 @@
           <t xml:space="preserve">    NonCurrent Deferred Revenue</t>
         </is>
       </c>
-      <c r="B82" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="B82" s="3" t="n">
+        <v>0</v>
       </c>
       <c r="C82" s="3" t="n">
         <v>0</v>
@@ -2715,10 +2627,8 @@
           <t xml:space="preserve">  NonCurrent Deferred Liabilities</t>
         </is>
       </c>
-      <c r="B83" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="B83" s="3" t="n">
+        <v>0</v>
       </c>
       <c r="C83" s="3" t="n">
         <v>0</v>
@@ -2743,10 +2653,8 @@
           <t xml:space="preserve">  NonCurrent Deferred Income Tax</t>
         </is>
       </c>
-      <c r="B84" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="B84" s="3" t="n">
+        <v>0</v>
       </c>
       <c r="C84" s="3" t="n">
         <v>0</v>
@@ -2771,10 +2679,8 @@
           <t xml:space="preserve">  Other Long-Term Liabilities</t>
         </is>
       </c>
-      <c r="B85" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="B85" s="3" t="n">
+        <v>0</v>
       </c>
       <c r="C85" s="3" t="n">
         <v>0</v>
@@ -2831,16 +2737,14 @@
           <t>Total Liabilities</t>
         </is>
       </c>
-      <c r="B87" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="B87" s="3" t="n">
+        <v>0.005575</v>
       </c>
       <c r="C87" s="3" t="n">
-        <v>0.011021</v>
+        <v>0.014021</v>
       </c>
       <c r="D87" s="3" t="n">
-        <v>0.014021</v>
+        <v>0.013712</v>
       </c>
       <c r="E87" s="1" t="inlineStr">
         <is>
@@ -2859,16 +2763,14 @@
           <t xml:space="preserve">  Common Stock</t>
         </is>
       </c>
-      <c r="B88" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="B88" s="3" t="n">
+        <v>0.225</v>
       </c>
       <c r="C88" s="3" t="n">
         <v>0.427079</v>
       </c>
       <c r="D88" s="3" t="n">
-        <v>0.427079</v>
+        <v>0.451481</v>
       </c>
       <c r="E88" s="1" t="inlineStr">
         <is>
@@ -2887,10 +2789,8 @@
           <t xml:space="preserve">  Preferred Stock</t>
         </is>
       </c>
-      <c r="B89" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="B89" s="3" t="n">
+        <v>0</v>
       </c>
       <c r="C89" s="3" t="n">
         <v>0</v>
@@ -2943,10 +2843,8 @@
           <t xml:space="preserve">  Accumulated other comprehensive income (loss)</t>
         </is>
       </c>
-      <c r="B91" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="B91" s="3" t="n">
+        <v>0</v>
       </c>
       <c r="C91" s="3" t="n">
         <v>0</v>
@@ -2971,10 +2869,8 @@
           <t xml:space="preserve">  Additional Paid-In Capital</t>
         </is>
       </c>
-      <c r="B92" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="B92" s="3" t="n">
+        <v>0</v>
       </c>
       <c r="C92" s="3" t="n">
         <v>0</v>
@@ -2999,10 +2895,8 @@
           <t xml:space="preserve">  Treasury Stock</t>
         </is>
       </c>
-      <c r="B93" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="B93" s="3" t="n">
+        <v>0</v>
       </c>
       <c r="C93" s="3" t="n">
         <v>0</v>
@@ -3027,16 +2921,14 @@
           <t xml:space="preserve">  Total Stockholders Equity</t>
         </is>
       </c>
-      <c r="B94" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="B94" s="3" t="n">
+        <v>0.216652</v>
       </c>
       <c r="C94" s="3" t="n">
-        <v>0.388691</v>
+        <v>0.337391</v>
       </c>
       <c r="D94" s="3" t="n">
-        <v>0.337391</v>
+        <v>0.306835</v>
       </c>
       <c r="E94" s="1" t="inlineStr">
         <is>
@@ -3055,10 +2947,8 @@
           <t xml:space="preserve">  Minority Interest</t>
         </is>
       </c>
-      <c r="B95" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="B95" s="3" t="n">
+        <v>0</v>
       </c>
       <c r="C95" s="3" t="n">
         <v>0</v>
@@ -3083,16 +2973,14 @@
           <t>Total Equity</t>
         </is>
       </c>
-      <c r="B96" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="B96" s="3" t="n">
+        <v>0.216652</v>
       </c>
       <c r="C96" s="3" t="n">
-        <v>0.388691</v>
+        <v>0.337391</v>
       </c>
       <c r="D96" s="3" t="n">
-        <v>0.337391</v>
+        <v>0.306835</v>
       </c>
       <c r="E96" s="1" t="inlineStr">
         <is>
@@ -3111,16 +2999,14 @@
           <t>Equity-to-Asset</t>
         </is>
       </c>
-      <c r="B97" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="B97" s="3" t="n">
+        <v>0.9749130393696536</v>
       </c>
       <c r="C97" s="3" t="n">
-        <v>0.9724276479064927</v>
+        <v>0.9601009641105027</v>
       </c>
       <c r="D97" s="3" t="n">
-        <v>0.9601009641105027</v>
+        <v>0.9572231217262991</v>
       </c>
       <c r="E97" s="1" t="inlineStr">
         <is>
@@ -3985,7 +3871,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:I90"/>
+  <dimension ref="A1:I118"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="16" customWidth="1" min="1" max="1"/>
@@ -4047,31 +3933,23 @@
           <t>balance_sheet</t>
         </is>
       </c>
-      <c r="B2" t="inlineStr">
-        <is>
-          <t>Current assets</t>
-        </is>
-      </c>
+      <c r="B2" t="inlineStr"/>
       <c r="C2" t="inlineStr">
         <is>
-          <t>Cash</t>
-        </is>
-      </c>
-      <c r="D2" t="inlineStr">
-        <is>
-          <t>CashAndCashEquivalents</t>
-        </is>
-      </c>
+          <t>AS AT JULY</t>
+        </is>
+      </c>
+      <c r="D2" t="inlineStr"/>
       <c r="E2" t="inlineStr">
         <is>
           <t>-</t>
         </is>
       </c>
       <c r="F2" s="5" t="n">
-        <v>0.399712</v>
+        <v>3.1e-05</v>
       </c>
       <c r="G2" s="5" t="n">
-        <v>0.351412</v>
+        <v>3.1e-05</v>
       </c>
       <c r="H2" t="inlineStr">
         <is>
@@ -4097,12 +3975,12 @@
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>Total assets</t>
+          <t>Cash 282,044</t>
         </is>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>TotalAssets</t>
+          <t>CashAndCashEquivalents</t>
         </is>
       </c>
       <c r="E3" t="inlineStr">
@@ -4110,11 +3988,13 @@
           <t>-</t>
         </is>
       </c>
-      <c r="F3" s="5" t="n">
-        <v>0.399712</v>
+      <c r="F3" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="G3" s="5" t="n">
-        <v>0.351412</v>
+        <v>0.320547</v>
       </c>
       <c r="H3" t="inlineStr">
         <is>
@@ -4135,17 +4015,17 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>Current liabilities</t>
+          <t>Current assets</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>Accounts payable and accrued liabilities (Notes 4 and 6)</t>
+          <t>Total assets 282,044</t>
         </is>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>PayablesAndAccruedExpenses</t>
+          <t>TotalAssets</t>
         </is>
       </c>
       <c r="E4" t="inlineStr">
@@ -4153,11 +4033,13 @@
           <t>-</t>
         </is>
       </c>
-      <c r="F4" s="5" t="n">
-        <v>0.011021</v>
+      <c r="F4" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="G4" s="5" t="n">
-        <v>0.014021</v>
+        <v>0.320547</v>
       </c>
       <c r="H4" t="inlineStr">
         <is>
@@ -4183,12 +4065,12 @@
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>Total liabilities</t>
+          <t>Accounts payable and accrued liabilities (Notes 4 and 6) 13,711</t>
         </is>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>TotalLiabilities</t>
+          <t>PayablesAndAccruedExpenses</t>
         </is>
       </c>
       <c r="E5" t="inlineStr">
@@ -4196,11 +4078,13 @@
           <t>-</t>
         </is>
       </c>
-      <c r="F5" s="5" t="n">
-        <v>0.011021</v>
+      <c r="F5" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="G5" s="5" t="n">
-        <v>0.014021</v>
+        <v>0.013712</v>
       </c>
       <c r="H5" t="inlineStr">
         <is>
@@ -4221,17 +4105,17 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>Shareholders’ equity</t>
+          <t>Current liabilities</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>Share capital (Note 5)</t>
+          <t>Total liabilities 13,711</t>
         </is>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>CapitalStock</t>
+          <t>TotalLiabilities</t>
         </is>
       </c>
       <c r="E6" t="inlineStr">
@@ -4239,11 +4123,13 @@
           <t>-</t>
         </is>
       </c>
-      <c r="F6" s="5" t="n">
-        <v>0.427079</v>
+      <c r="F6" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="G6" s="5" t="n">
-        <v>0.427079</v>
+        <v>0.013712</v>
       </c>
       <c r="H6" t="inlineStr">
         <is>
@@ -4269,20 +4155,24 @@
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>Equity reserves (Note 5)</t>
-        </is>
-      </c>
-      <c r="D7" t="inlineStr"/>
+          <t>Share capital (Note 5) 451,481</t>
+        </is>
+      </c>
+      <c r="D7" t="inlineStr">
+        <is>
+          <t>CapitalStock</t>
+        </is>
+      </c>
       <c r="E7" t="inlineStr">
         <is>
           <t>-</t>
         </is>
       </c>
       <c r="F7" s="5" t="n">
-        <v>0.047333</v>
+        <v>0.427079</v>
       </c>
       <c r="G7" s="5" t="n">
-        <v>0.047333</v>
+        <v>0.451481</v>
       </c>
       <c r="H7" t="inlineStr">
         <is>
@@ -4308,24 +4198,20 @@
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>Deficit</t>
-        </is>
-      </c>
-      <c r="D8" t="inlineStr">
-        <is>
-          <t>RetainedEarnings</t>
-        </is>
-      </c>
+          <t>Equity reserves (Note 5) 37,931</t>
+        </is>
+      </c>
+      <c r="D8" t="inlineStr"/>
       <c r="E8" t="inlineStr">
         <is>
           <t>-</t>
         </is>
       </c>
       <c r="F8" s="5" t="n">
-        <v>-0.08572100000000001</v>
+        <v>0.047333</v>
       </c>
       <c r="G8" s="5" t="n">
-        <v>-0.137021</v>
+        <v>0.037931</v>
       </c>
       <c r="H8" t="inlineStr">
         <is>
@@ -4351,24 +4237,22 @@
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>Total shareholders’ equity</t>
-        </is>
-      </c>
-      <c r="D9" t="inlineStr">
-        <is>
-          <t>StockholdersEquity</t>
-        </is>
-      </c>
+          <t>Deficit (221,079)</t>
+        </is>
+      </c>
+      <c r="D9" t="inlineStr"/>
       <c r="E9" t="inlineStr">
         <is>
           <t>-</t>
         </is>
       </c>
-      <c r="F9" s="5" t="n">
-        <v>0.388691</v>
+      <c r="F9" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="G9" s="5" t="n">
-        <v>0.337391</v>
+        <v>-0.182577</v>
       </c>
       <c r="H9" t="inlineStr">
         <is>
@@ -4394,12 +4278,12 @@
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>Total liabilities and shareholders’ equity</t>
+          <t>Total shareholders’ equity 268,333</t>
         </is>
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>TotalLiabilitiesAndTotalEquityGrossMinorityInterest</t>
+          <t>StockholdersEquity</t>
         </is>
       </c>
       <c r="E10" t="inlineStr">
@@ -4407,11 +4291,13 @@
           <t>-</t>
         </is>
       </c>
-      <c r="F10" s="5" t="n">
-        <v>0.399712</v>
+      <c r="F10" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="G10" s="5" t="n">
-        <v>0.351412</v>
+        <v>0.306835</v>
       </c>
       <c r="H10" t="inlineStr">
         <is>
@@ -4427,22 +4313,22 @@
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>cash_flow</t>
+          <t>balance_sheet</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>CASH FLOWS FROM OPERATING ACTIVITIES</t>
+          <t>Shareholders’ equity</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>Loss for the year</t>
+          <t>Total liabilities and shareholders’ equity 282,044</t>
         </is>
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>NetIncomeFromContinuingOperations</t>
+          <t>TotalLiabilitiesAndTotalEquityGrossMinorityInterest</t>
         </is>
       </c>
       <c r="E11" t="inlineStr">
@@ -4456,73 +4342,75 @@
         </is>
       </c>
       <c r="G11" s="5" t="n">
-        <v>-0.0513</v>
-      </c>
-      <c r="H11" s="5" t="n">
-        <v>-0.045556</v>
-      </c>
-      <c r="I11" s="5" t="n">
-        <v>-0.038502</v>
+        <v>0.320547</v>
+      </c>
+      <c r="H11" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="I11" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>cash_flow</t>
+          <t>balance_sheet</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>Changes in non-cash working capital item</t>
+          <t>Shareholders’ equity</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>Accounts payable and accrued liabilities</t>
-        </is>
-      </c>
-      <c r="D12" t="inlineStr">
-        <is>
-          <t>ChangeInPayablesAndAccruedExpense</t>
-        </is>
-      </c>
-      <c r="E12" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+          <t>Basis of presentation (Note</t>
+        </is>
+      </c>
+      <c r="D12" t="inlineStr"/>
+      <c r="E12" s="5" t="n">
+        <v>2e-06</v>
       </c>
       <c r="F12" s="5" t="n">
-        <v>0.005446</v>
+        <v>2e-06</v>
       </c>
       <c r="G12" s="5" t="n">
-        <v>0.003</v>
-      </c>
-      <c r="H12" s="5" t="n">
-        <v>-0.000309</v>
-      </c>
-      <c r="I12" s="5" t="n">
-        <v>-1e-06</v>
+        <v>2e-06</v>
+      </c>
+      <c r="H12" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="I12" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>cash_flow</t>
+          <t>balance_sheet</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>Changes in non-cash working capital item</t>
+          <t>Current assets</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>Net cash used in operating activities</t>
+          <t>Cash 320,547</t>
         </is>
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>OperatingCashFlow</t>
+          <t>CashAndCashEquivalents</t>
         </is>
       </c>
       <c r="E13" t="inlineStr">
@@ -4531,52 +4419,62 @@
         </is>
       </c>
       <c r="F13" s="5" t="n">
-        <v>-0.033996</v>
-      </c>
-      <c r="G13" s="5" t="n">
-        <v>-0.0483</v>
-      </c>
-      <c r="H13" s="5" t="n">
-        <v>-0.045865</v>
-      </c>
-      <c r="I13" s="5" t="n">
-        <v>-0.038503</v>
+        <v>0.351412</v>
+      </c>
+      <c r="G13" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="H13" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="I13" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>cash_flow</t>
+          <t>balance_sheet</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>CASH FLOWS FROM FINANCING ACTIVITIES</t>
+          <t>Current assets</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>Proceeds from exercise of warrants</t>
-        </is>
-      </c>
-      <c r="D14" t="inlineStr"/>
+          <t>Total assets 320,547</t>
+        </is>
+      </c>
+      <c r="D14" t="inlineStr">
+        <is>
+          <t>TotalAssets</t>
+        </is>
+      </c>
       <c r="E14" t="inlineStr">
         <is>
           <t>-</t>
         </is>
       </c>
-      <c r="F14" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="F14" s="5" t="n">
+        <v>0.351412</v>
       </c>
       <c r="G14" t="inlineStr">
         <is>
           <t>-</t>
         </is>
       </c>
-      <c r="H14" s="5" t="n">
-        <v>0.015</v>
+      <c r="H14" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="I14" t="inlineStr">
         <is>
@@ -4587,22 +4485,22 @@
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>cash_flow</t>
+          <t>balance_sheet</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>CASH FLOWS FROM FINANCING ACTIVITIES</t>
+          <t>Current liabilities</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>Net cash provided by financing activities</t>
+          <t>Accounts payable and accrued liabilities (Notes 4 and 6) 13,712</t>
         </is>
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>FinancingCashFlow</t>
+          <t>PayablesAndAccruedExpenses</t>
         </is>
       </c>
       <c r="E15" t="inlineStr">
@@ -4611,15 +4509,17 @@
         </is>
       </c>
       <c r="F15" s="5" t="n">
-        <v>0.220481</v>
+        <v>0.014021</v>
       </c>
       <c r="G15" t="inlineStr">
         <is>
           <t>-</t>
         </is>
       </c>
-      <c r="H15" s="5" t="n">
-        <v>0.015</v>
+      <c r="H15" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="I15" t="inlineStr">
         <is>
@@ -4630,22 +4530,22 @@
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>cash_flow</t>
+          <t>balance_sheet</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>CASH FLOWS FROM FINANCING ACTIVITIES</t>
+          <t>Current liabilities</t>
         </is>
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>Change in cash during the year</t>
+          <t>Total liabilities 13,712</t>
         </is>
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>ChangesInCash</t>
+          <t>TotalLiabilities</t>
         </is>
       </c>
       <c r="E16" t="inlineStr">
@@ -4654,76 +4554,84 @@
         </is>
       </c>
       <c r="F16" s="5" t="n">
-        <v>0.186485</v>
-      </c>
-      <c r="G16" s="5" t="n">
-        <v>-0.0483</v>
-      </c>
-      <c r="H16" s="5" t="n">
-        <v>-0.030865</v>
-      </c>
-      <c r="I16" s="5" t="n">
-        <v>-0.038503</v>
+        <v>0.014021</v>
+      </c>
+      <c r="G16" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="H16" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="I16" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>cash_flow</t>
+          <t>balance_sheet</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>CASH FLOWS FROM FINANCING ACTIVITIES</t>
+          <t>Shareholders’ equity</t>
         </is>
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>Cash, beginning of year</t>
-        </is>
-      </c>
-      <c r="D17" t="inlineStr">
-        <is>
-          <t>BeginningCashPosition</t>
-        </is>
-      </c>
+          <t>Deficit (182,577)</t>
+        </is>
+      </c>
+      <c r="D17" t="inlineStr"/>
       <c r="E17" t="inlineStr">
         <is>
           <t>-</t>
         </is>
       </c>
       <c r="F17" s="5" t="n">
-        <v>0.213227</v>
-      </c>
-      <c r="G17" s="5" t="n">
-        <v>0.399712</v>
-      </c>
-      <c r="H17" s="5" t="n">
-        <v>0.351412</v>
-      </c>
-      <c r="I17" s="5" t="n">
-        <v>0.320547</v>
+        <v>-0.137021</v>
+      </c>
+      <c r="G17" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="H17" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="I17" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>cash_flow</t>
+          <t>balance_sheet</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>CASH FLOWS FROM FINANCING ACTIVITIES</t>
+          <t>Shareholders’ equity</t>
         </is>
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>Cash, end of year</t>
+          <t>Total shareholders’ equity 306,835</t>
         </is>
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t>EndCashPosition</t>
+          <t>StockholdersEquity</t>
         </is>
       </c>
       <c r="E18" t="inlineStr">
@@ -4732,74 +4640,88 @@
         </is>
       </c>
       <c r="F18" s="5" t="n">
-        <v>0.399712</v>
-      </c>
-      <c r="G18" s="5" t="n">
-        <v>0.351412</v>
-      </c>
-      <c r="H18" s="5" t="n">
-        <v>0.320547</v>
-      </c>
-      <c r="I18" s="5" t="n">
-        <v>0.282044</v>
+        <v>0.337391</v>
+      </c>
+      <c r="G18" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="H18" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="I18" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>cash_flow</t>
+          <t>balance_sheet</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>Non-cash investing and financing activities</t>
+          <t>Shareholders’ equity</t>
         </is>
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>In addition to cash proceeds of $15,000, share capital includes a $9,402 non-cash transfer from equity reserves, being the grant-date fair value of 100,000 warrants exercised in year ended July</t>
-        </is>
-      </c>
-      <c r="D19" t="inlineStr"/>
+          <t>Total liabilities and shareholders’ equity 320,547</t>
+        </is>
+      </c>
+      <c r="D19" t="inlineStr">
+        <is>
+          <t>TotalLiabilitiesAndTotalEquityGrossMinorityInterest</t>
+        </is>
+      </c>
       <c r="E19" t="inlineStr">
         <is>
           <t>-</t>
         </is>
       </c>
-      <c r="F19" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="G19" s="5" t="n">
-        <v>0.002024</v>
-      </c>
-      <c r="H19" s="5" t="n">
-        <v>0.002024</v>
-      </c>
-      <c r="I19" s="5" t="n">
-        <v>3.1e-05</v>
+      <c r="F19" s="5" t="n">
+        <v>0.351412</v>
+      </c>
+      <c r="G19" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="H19" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="I19" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>cash_flow</t>
+          <t>balance_sheet</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>CASH FLOWS FROM OPERATING ACTIVITIES</t>
+          <t>Current assets</t>
         </is>
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>Net loss for the year</t>
+          <t>Cash</t>
         </is>
       </c>
       <c r="D20" t="inlineStr">
         <is>
-          <t>NetIncomeFromContinuingOperations</t>
+          <t>CashAndCashEquivalents</t>
         </is>
       </c>
       <c r="E20" t="inlineStr">
@@ -4808,10 +4730,10 @@
         </is>
       </c>
       <c r="F20" s="5" t="n">
-        <v>-0.077373</v>
+        <v>0.399712</v>
       </c>
       <c r="G20" s="5" t="n">
-        <v>-0.0513</v>
+        <v>0.351412</v>
       </c>
       <c r="H20" t="inlineStr">
         <is>
@@ -4827,22 +4749,22 @@
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>cash_flow</t>
+          <t>balance_sheet</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>Non-cash expenses</t>
+          <t>Current assets</t>
         </is>
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>Share-based compensation</t>
+          <t>Total assets</t>
         </is>
       </c>
       <c r="D21" t="inlineStr">
         <is>
-          <t>StockBasedCompensation</t>
+          <t>TotalAssets</t>
         </is>
       </c>
       <c r="E21" t="inlineStr">
@@ -4851,12 +4773,10 @@
         </is>
       </c>
       <c r="F21" s="5" t="n">
-        <v>0.037931</v>
-      </c>
-      <c r="G21" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+        <v>0.399712</v>
+      </c>
+      <c r="G21" s="5" t="n">
+        <v>0.351412</v>
       </c>
       <c r="H21" t="inlineStr">
         <is>
@@ -4872,22 +4792,22 @@
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>cash_flow</t>
+          <t>balance_sheet</t>
         </is>
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>CASH FLOWS FROM FINANCING ACTIVITIES</t>
+          <t>Current liabilities</t>
         </is>
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>Proceeds from sale of shares</t>
+          <t>Accounts payable and accrued liabilities (Notes 4 and 6)</t>
         </is>
       </c>
       <c r="D22" t="inlineStr">
         <is>
-          <t>CommonStockIssuance</t>
+          <t>PayablesAndAccruedExpenses</t>
         </is>
       </c>
       <c r="E22" t="inlineStr">
@@ -4896,12 +4816,10 @@
         </is>
       </c>
       <c r="F22" s="5" t="n">
-        <v>0.3225</v>
-      </c>
-      <c r="G22" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+        <v>0.011021</v>
+      </c>
+      <c r="G22" s="5" t="n">
+        <v>0.014021</v>
       </c>
       <c r="H22" t="inlineStr">
         <is>
@@ -4917,22 +4835,22 @@
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>cash_flow</t>
+          <t>balance_sheet</t>
         </is>
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>CASH FLOWS FROM FINANCING ACTIVITIES</t>
+          <t>Current liabilities</t>
         </is>
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>Payments for share issuance costs</t>
+          <t>Total liabilities</t>
         </is>
       </c>
       <c r="D23" t="inlineStr">
         <is>
-          <t>NetOtherFinancingCharges</t>
+          <t>TotalLiabilities</t>
         </is>
       </c>
       <c r="E23" t="inlineStr">
@@ -4941,12 +4859,10 @@
         </is>
       </c>
       <c r="F23" s="5" t="n">
-        <v>-0.102019</v>
-      </c>
-      <c r="G23" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+        <v>0.011021</v>
+      </c>
+      <c r="G23" s="5" t="n">
+        <v>0.014021</v>
       </c>
       <c r="H23" t="inlineStr">
         <is>
@@ -4962,30 +4878,34 @@
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>cash_flow</t>
+          <t>balance_sheet</t>
         </is>
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t>Non-cash investing and financing activities</t>
+          <t>Shareholders’ equity</t>
         </is>
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>non-cash costs for the fair value of warrants issued in connection with the Company’s initial public offering and $111,019 in cash costs of which $9,000 was paid in the period from incorporation on March 3, 2021 to July</t>
-        </is>
-      </c>
-      <c r="D24" t="inlineStr"/>
+          <t>Share capital (Note 5)</t>
+        </is>
+      </c>
+      <c r="D24" t="inlineStr">
+        <is>
+          <t>CapitalStock</t>
+        </is>
+      </c>
       <c r="E24" t="inlineStr">
         <is>
           <t>-</t>
         </is>
       </c>
       <c r="F24" s="5" t="n">
-        <v>0.002021</v>
+        <v>0.427079</v>
       </c>
       <c r="G24" s="5" t="n">
-        <v>3.1e-05</v>
+        <v>0.427079</v>
       </c>
       <c r="H24" t="inlineStr">
         <is>
@@ -5001,32 +4921,30 @@
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>cash_flow</t>
+          <t>balance_sheet</t>
         </is>
       </c>
       <c r="B25" t="inlineStr">
         <is>
-          <t>CASH FLOWS FROM OPERATING ACTIVITIES</t>
+          <t>Shareholders’ equity</t>
         </is>
       </c>
       <c r="C25" t="inlineStr">
         <is>
-          <t>Net loss for the period (77,373)</t>
+          <t>Equity reserves (Note 5)</t>
         </is>
       </c>
       <c r="D25" t="inlineStr"/>
-      <c r="E25" s="5" t="n">
-        <v>-0.008348</v>
-      </c>
-      <c r="F25" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="G25" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="E25" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="F25" s="5" t="n">
+        <v>0.047333</v>
+      </c>
+      <c r="G25" s="5" t="n">
+        <v>0.047333</v>
       </c>
       <c r="H25" t="inlineStr">
         <is>
@@ -5042,22 +4960,22 @@
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>cash_flow</t>
+          <t>balance_sheet</t>
         </is>
       </c>
       <c r="B26" t="inlineStr">
         <is>
-          <t>Non-cash expenses</t>
+          <t>Shareholders’ equity</t>
         </is>
       </c>
       <c r="C26" t="inlineStr">
         <is>
-          <t>Share-based compensation 37,931</t>
+          <t>Deficit</t>
         </is>
       </c>
       <c r="D26" t="inlineStr">
         <is>
-          <t>StockBasedCompensation</t>
+          <t>RetainedEarnings</t>
         </is>
       </c>
       <c r="E26" t="inlineStr">
@@ -5065,15 +4983,11 @@
           <t>-</t>
         </is>
       </c>
-      <c r="F26" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="G26" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="F26" s="5" t="n">
+        <v>-0.08572100000000001</v>
+      </c>
+      <c r="G26" s="5" t="n">
+        <v>-0.137021</v>
       </c>
       <c r="H26" t="inlineStr">
         <is>
@@ -5089,36 +5003,34 @@
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>cash_flow</t>
+          <t>balance_sheet</t>
         </is>
       </c>
       <c r="B27" t="inlineStr">
         <is>
-          <t>Changes in non-cash working capital items</t>
+          <t>Shareholders’ equity</t>
         </is>
       </c>
       <c r="C27" t="inlineStr">
         <is>
-          <t>Accounts payable and accrued liabilities 5,446</t>
+          <t>Total shareholders’ equity</t>
         </is>
       </c>
       <c r="D27" t="inlineStr">
         <is>
-          <t>ChangeInPayablesAndAccruedExpense</t>
-        </is>
-      </c>
-      <c r="E27" s="5" t="n">
-        <v>0.005575</v>
-      </c>
-      <c r="F27" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="G27" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+          <t>StockholdersEquity</t>
+        </is>
+      </c>
+      <c r="E27" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="F27" s="5" t="n">
+        <v>0.388691</v>
+      </c>
+      <c r="G27" s="5" t="n">
+        <v>0.337391</v>
       </c>
       <c r="H27" t="inlineStr">
         <is>
@@ -5134,36 +5046,34 @@
     <row r="28">
       <c r="A28" t="inlineStr">
         <is>
-          <t>cash_flow</t>
+          <t>balance_sheet</t>
         </is>
       </c>
       <c r="B28" t="inlineStr">
         <is>
-          <t>Changes in non-cash working capital items</t>
+          <t>Shareholders’ equity</t>
         </is>
       </c>
       <c r="C28" t="inlineStr">
         <is>
-          <t>Net cash used in operating activities (33,996)</t>
+          <t>Total liabilities and shareholders’ equity</t>
         </is>
       </c>
       <c r="D28" t="inlineStr">
         <is>
-          <t>OperatingCashFlow</t>
-        </is>
-      </c>
-      <c r="E28" s="5" t="n">
-        <v>-0.002773</v>
-      </c>
-      <c r="F28" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="G28" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+          <t>TotalLiabilitiesAndTotalEquityGrossMinorityInterest</t>
+        </is>
+      </c>
+      <c r="E28" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="F28" s="5" t="n">
+        <v>0.399712</v>
+      </c>
+      <c r="G28" s="5" t="n">
+        <v>0.351412</v>
       </c>
       <c r="H28" t="inlineStr">
         <is>
@@ -5179,26 +5089,26 @@
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
-          <t>cash_flow</t>
+          <t>balance_sheet</t>
         </is>
       </c>
       <c r="B29" t="inlineStr">
         <is>
-          <t>CASH FLOWS FROM FINANCING ACTIVITIES</t>
+          <t>Current assets</t>
         </is>
       </c>
       <c r="C29" t="inlineStr">
         <is>
-          <t>Proceeds from sale of shares 322,500</t>
+          <t>Cash 399,712</t>
         </is>
       </c>
       <c r="D29" t="inlineStr">
         <is>
-          <t>CommonStockIssuance</t>
+          <t>CashAndCashEquivalents</t>
         </is>
       </c>
       <c r="E29" s="5" t="n">
-        <v>0.225</v>
+        <v>0.213227</v>
       </c>
       <c r="F29" t="inlineStr">
         <is>
@@ -5224,22 +5134,22 @@
     <row r="30">
       <c r="A30" t="inlineStr">
         <is>
-          <t>cash_flow</t>
+          <t>balance_sheet</t>
         </is>
       </c>
       <c r="B30" t="inlineStr">
         <is>
-          <t>CASH FLOWS FROM FINANCING ACTIVITIES</t>
+          <t>Current assets</t>
         </is>
       </c>
       <c r="C30" t="inlineStr">
         <is>
-          <t>Payments for share issuance costs (102,019)</t>
+          <t>Deferred financing fees (Note 5) -</t>
         </is>
       </c>
       <c r="D30" t="inlineStr"/>
       <c r="E30" s="5" t="n">
-        <v>-0.008999999999999999</v>
+        <v>0.008999999999999999</v>
       </c>
       <c r="F30" t="inlineStr">
         <is>
@@ -5265,26 +5175,26 @@
     <row r="31">
       <c r="A31" t="inlineStr">
         <is>
-          <t>cash_flow</t>
+          <t>balance_sheet</t>
         </is>
       </c>
       <c r="B31" t="inlineStr">
         <is>
-          <t>CASH FLOWS FROM FINANCING ACTIVITIES</t>
+          <t>Current assets</t>
         </is>
       </c>
       <c r="C31" t="inlineStr">
         <is>
-          <t>Net cash provided by financing activities 220,481</t>
+          <t>Total assets 399,712</t>
         </is>
       </c>
       <c r="D31" t="inlineStr">
         <is>
-          <t>FinancingCashFlow</t>
+          <t>TotalAssets</t>
         </is>
       </c>
       <c r="E31" s="5" t="n">
-        <v>0.216</v>
+        <v>0.222227</v>
       </c>
       <c r="F31" t="inlineStr">
         <is>
@@ -5310,26 +5220,26 @@
     <row r="32">
       <c r="A32" t="inlineStr">
         <is>
-          <t>cash_flow</t>
+          <t>balance_sheet</t>
         </is>
       </c>
       <c r="B32" t="inlineStr">
         <is>
-          <t>CASH FLOWS FROM FINANCING ACTIVITIES</t>
+          <t>Current liabilities</t>
         </is>
       </c>
       <c r="C32" t="inlineStr">
         <is>
-          <t>Change in cash during the period 186,485</t>
+          <t>Accounts payable and accrued liabilities (Notes 4 and 6) 11,021</t>
         </is>
       </c>
       <c r="D32" t="inlineStr">
         <is>
-          <t>ChangesInCash</t>
+          <t>PayablesAndAccruedExpenses</t>
         </is>
       </c>
       <c r="E32" s="5" t="n">
-        <v>0.213227</v>
+        <v>0.005575</v>
       </c>
       <c r="F32" t="inlineStr">
         <is>
@@ -5355,28 +5265,26 @@
     <row r="33">
       <c r="A33" t="inlineStr">
         <is>
-          <t>cash_flow</t>
+          <t>balance_sheet</t>
         </is>
       </c>
       <c r="B33" t="inlineStr">
         <is>
-          <t>CASH FLOWS FROM FINANCING ACTIVITIES</t>
+          <t>Current liabilities</t>
         </is>
       </c>
       <c r="C33" t="inlineStr">
         <is>
-          <t>Cash, beginning of period 213,227</t>
+          <t>Total liabilities 11,021</t>
         </is>
       </c>
       <c r="D33" t="inlineStr">
         <is>
-          <t>BeginningCashPosition</t>
-        </is>
-      </c>
-      <c r="E33" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+          <t>TotalLiabilities</t>
+        </is>
+      </c>
+      <c r="E33" s="5" t="n">
+        <v>0.005575</v>
       </c>
       <c r="F33" t="inlineStr">
         <is>
@@ -5402,26 +5310,26 @@
     <row r="34">
       <c r="A34" t="inlineStr">
         <is>
-          <t>cash_flow</t>
+          <t>balance_sheet</t>
         </is>
       </c>
       <c r="B34" t="inlineStr">
         <is>
-          <t>CASH FLOWS FROM FINANCING ACTIVITIES</t>
+          <t>Shareholders’ equity</t>
         </is>
       </c>
       <c r="C34" t="inlineStr">
         <is>
-          <t>Cash, end of period 399,712</t>
+          <t>Share capital (Note 5) 427,079</t>
         </is>
       </c>
       <c r="D34" t="inlineStr">
         <is>
-          <t>EndCashPosition</t>
+          <t>CapitalStock</t>
         </is>
       </c>
       <c r="E34" s="5" t="n">
-        <v>0.213227</v>
+        <v>0.225</v>
       </c>
       <c r="F34" t="inlineStr">
         <is>
@@ -5447,22 +5355,24 @@
     <row r="35">
       <c r="A35" t="inlineStr">
         <is>
-          <t>cash_flow</t>
+          <t>balance_sheet</t>
         </is>
       </c>
       <c r="B35" t="inlineStr">
         <is>
-          <t>Non-cash investing and financing activities</t>
+          <t>Shareholders’ equity</t>
         </is>
       </c>
       <c r="C35" t="inlineStr">
         <is>
-          <t>A total of $120,421 was recognized for share issuance costs in the year ended July 31, 2022. This amount includes</t>
+          <t>Equity reserves (Note 5) 47,333</t>
         </is>
       </c>
       <c r="D35" t="inlineStr"/>
-      <c r="E35" s="5" t="n">
-        <v>0.009402000000000001</v>
+      <c r="E35" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="F35" t="inlineStr">
         <is>
@@ -5488,22 +5398,22 @@
     <row r="36">
       <c r="A36" t="inlineStr">
         <is>
-          <t>cash_flow</t>
+          <t>balance_sheet</t>
         </is>
       </c>
       <c r="B36" t="inlineStr">
         <is>
-          <t>Non-cash investing and financing activities</t>
+          <t>Shareholders’ equity</t>
         </is>
       </c>
       <c r="C36" t="inlineStr">
         <is>
-          <t>non-cash costs for the fair value of warrants issued in connection with the Company’s initial public offering and</t>
+          <t>Deficit (85,721)</t>
         </is>
       </c>
       <c r="D36" t="inlineStr"/>
       <c r="E36" s="5" t="n">
-        <v>0.111019</v>
+        <v>-0.008348</v>
       </c>
       <c r="F36" t="inlineStr">
         <is>
@@ -5529,26 +5439,36 @@
     <row r="37">
       <c r="A37" t="inlineStr">
         <is>
-          <t>income_statement</t>
-        </is>
-      </c>
-      <c r="B37" t="inlineStr"/>
+          <t>balance_sheet</t>
+        </is>
+      </c>
+      <c r="B37" t="inlineStr">
+        <is>
+          <t>Shareholders’ equity</t>
+        </is>
+      </c>
       <c r="C37" t="inlineStr">
         <is>
-          <t>FOR THE YEARS ENDED JULY</t>
-        </is>
-      </c>
-      <c r="D37" t="inlineStr"/>
-      <c r="E37" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="F37" s="5" t="n">
-        <v>3.1e-05</v>
-      </c>
-      <c r="G37" s="5" t="n">
-        <v>3.1e-05</v>
+          <t>Total shareholders’ equity 388,691</t>
+        </is>
+      </c>
+      <c r="D37" t="inlineStr">
+        <is>
+          <t>StockholdersEquity</t>
+        </is>
+      </c>
+      <c r="E37" s="5" t="n">
+        <v>0.216652</v>
+      </c>
+      <c r="F37" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="G37" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="H37" t="inlineStr">
         <is>
@@ -5564,28 +5484,36 @@
     <row r="38">
       <c r="A38" t="inlineStr">
         <is>
-          <t>income_statement</t>
+          <t>balance_sheet</t>
         </is>
       </c>
       <c r="B38" t="inlineStr">
         <is>
-          <t>EXPENSES</t>
+          <t>Shareholders’ equity</t>
         </is>
       </c>
       <c r="C38" t="inlineStr">
         <is>
-          <t>Administrative and corporate services (Note 6) 18,900</t>
-        </is>
-      </c>
-      <c r="D38" t="inlineStr"/>
+          <t>Total liabilities and shareholders’ equity 399,712</t>
+        </is>
+      </c>
+      <c r="D38" t="inlineStr">
+        <is>
+          <t>TotalLiabilitiesAndTotalEquityGrossMinorityInterest</t>
+        </is>
+      </c>
       <c r="E38" s="5" t="n">
-        <v>0.002835</v>
-      </c>
-      <c r="F38" s="5" t="n">
-        <v>0.0189</v>
-      </c>
-      <c r="G38" s="5" t="n">
-        <v>0.0189</v>
+        <v>0.222227</v>
+      </c>
+      <c r="F38" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="G38" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="H38" t="inlineStr">
         <is>
@@ -5601,22 +5529,22 @@
     <row r="39">
       <c r="A39" t="inlineStr">
         <is>
-          <t>income_statement</t>
+          <t>cash_flow</t>
         </is>
       </c>
       <c r="B39" t="inlineStr">
         <is>
-          <t>Transfer agent, shareholder communications, listing and</t>
+          <t>CASH FLOWS FROM OPERATING ACTIVITIES</t>
         </is>
       </c>
       <c r="C39" t="inlineStr">
         <is>
-          <t>Transfer agent, shareholder communications, listing and filing fees 15,789</t>
+          <t>Loss for the year</t>
         </is>
       </c>
       <c r="D39" t="inlineStr">
         <is>
-          <t>OtherOperatingExpenses</t>
+          <t>NetIncomeFromContinuingOperations</t>
         </is>
       </c>
       <c r="E39" t="inlineStr">
@@ -5630,38 +5558,34 @@
         </is>
       </c>
       <c r="G39" s="5" t="n">
-        <v>0.015965</v>
-      </c>
-      <c r="H39" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="I39" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+        <v>-0.0513</v>
+      </c>
+      <c r="H39" s="5" t="n">
+        <v>-0.045556</v>
+      </c>
+      <c r="I39" s="5" t="n">
+        <v>-0.038502</v>
       </c>
     </row>
     <row r="40">
       <c r="A40" t="inlineStr">
         <is>
-          <t>income_statement</t>
+          <t>cash_flow</t>
         </is>
       </c>
       <c r="B40" t="inlineStr">
         <is>
-          <t>Transfer agent, shareholder communications, listing and</t>
+          <t>Changes in non-cash working capital item</t>
         </is>
       </c>
       <c r="C40" t="inlineStr">
         <is>
-          <t>Professional fees 11,451</t>
+          <t>Accounts payable and accrued liabilities</t>
         </is>
       </c>
       <c r="D40" t="inlineStr">
         <is>
-          <t>ProfessionalExpenseAndContractServicesExpense</t>
+          <t>ChangeInPayablesAndAccruedExpense</t>
         </is>
       </c>
       <c r="E40" t="inlineStr">
@@ -5669,44 +5593,38 @@
           <t>-</t>
         </is>
       </c>
-      <c r="F40" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="F40" s="5" t="n">
+        <v>0.005446</v>
       </c>
       <c r="G40" s="5" t="n">
-        <v>0.011124</v>
-      </c>
-      <c r="H40" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="I40" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+        <v>0.003</v>
+      </c>
+      <c r="H40" s="5" t="n">
+        <v>-0.000309</v>
+      </c>
+      <c r="I40" s="5" t="n">
+        <v>-1e-06</v>
       </c>
     </row>
     <row r="41">
       <c r="A41" t="inlineStr">
         <is>
-          <t>income_statement</t>
+          <t>cash_flow</t>
         </is>
       </c>
       <c r="B41" t="inlineStr">
         <is>
-          <t>Transfer agent, shareholder communications, listing and</t>
+          <t>Changes in non-cash working capital item</t>
         </is>
       </c>
       <c r="C41" t="inlineStr">
         <is>
-          <t>Bank charges 75</t>
+          <t>Net cash used in operating activities</t>
         </is>
       </c>
       <c r="D41" t="inlineStr">
         <is>
-          <t>SellingGeneralAndAdministration</t>
+          <t>OperatingCashFlow</t>
         </is>
       </c>
       <c r="E41" t="inlineStr">
@@ -5714,39 +5632,33 @@
           <t>-</t>
         </is>
       </c>
-      <c r="F41" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="F41" s="5" t="n">
+        <v>-0.033996</v>
       </c>
       <c r="G41" s="5" t="n">
-        <v>7.2e-05</v>
-      </c>
-      <c r="H41" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="I41" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+        <v>-0.0483</v>
+      </c>
+      <c r="H41" s="5" t="n">
+        <v>-0.045865</v>
+      </c>
+      <c r="I41" s="5" t="n">
+        <v>-0.038503</v>
       </c>
     </row>
     <row r="42">
       <c r="A42" t="inlineStr">
         <is>
-          <t>income_statement</t>
+          <t>cash_flow</t>
         </is>
       </c>
       <c r="B42" t="inlineStr">
         <is>
-          <t>Transfer agent, shareholder communications, listing and</t>
+          <t>CASH FLOWS FROM FINANCING ACTIVITIES</t>
         </is>
       </c>
       <c r="C42" t="inlineStr">
         <is>
-          <t>Interest income (7,713)</t>
+          <t>Proceeds from exercise of warrants</t>
         </is>
       </c>
       <c r="D42" t="inlineStr"/>
@@ -5760,13 +5672,13 @@
           <t>-</t>
         </is>
       </c>
-      <c r="G42" s="5" t="n">
-        <v>-0.000505</v>
-      </c>
-      <c r="H42" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="G42" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="H42" s="5" t="n">
+        <v>0.015</v>
       </c>
       <c r="I42" t="inlineStr">
         <is>
@@ -5777,22 +5689,22 @@
     <row r="43">
       <c r="A43" t="inlineStr">
         <is>
-          <t>income_statement</t>
+          <t>cash_flow</t>
         </is>
       </c>
       <c r="B43" t="inlineStr">
         <is>
-          <t>Transfer agent, shareholder communications, listing and</t>
+          <t>CASH FLOWS FROM FINANCING ACTIVITIES</t>
         </is>
       </c>
       <c r="C43" t="inlineStr">
         <is>
-          <t>Loss and comprehensive loss for the year (38,502)</t>
+          <t>Net cash provided by financing activities</t>
         </is>
       </c>
       <c r="D43" t="inlineStr">
         <is>
-          <t>NetIncome</t>
+          <t>FinancingCashFlow</t>
         </is>
       </c>
       <c r="E43" t="inlineStr">
@@ -5800,18 +5712,16 @@
           <t>-</t>
         </is>
       </c>
-      <c r="F43" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="G43" s="5" t="n">
-        <v>-0.045556</v>
-      </c>
-      <c r="H43" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="F43" s="5" t="n">
+        <v>0.220481</v>
+      </c>
+      <c r="G43" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="H43" s="5" t="n">
+        <v>0.015</v>
       </c>
       <c r="I43" t="inlineStr">
         <is>
@@ -5822,138 +5732,134 @@
     <row r="44">
       <c r="A44" t="inlineStr">
         <is>
-          <t>income_statement</t>
+          <t>cash_flow</t>
         </is>
       </c>
       <c r="B44" t="inlineStr">
         <is>
-          <t>Transfer agent, shareholder communications, listing and</t>
+          <t>CASH FLOWS FROM FINANCING ACTIVITIES</t>
         </is>
       </c>
       <c r="C44" t="inlineStr">
         <is>
-          <t>Basic and diluted loss per common share (Note 5) (0.01)</t>
-        </is>
-      </c>
-      <c r="D44" t="inlineStr"/>
+          <t>Change in cash during the year</t>
+        </is>
+      </c>
+      <c r="D44" t="inlineStr">
+        <is>
+          <t>ChangesInCash</t>
+        </is>
+      </c>
       <c r="E44" t="inlineStr">
         <is>
           <t>-</t>
         </is>
       </c>
       <c r="F44" s="5" t="n">
-        <v>-1e-08</v>
+        <v>0.186485</v>
       </c>
       <c r="G44" s="5" t="n">
-        <v>-1e-08</v>
-      </c>
-      <c r="H44" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="I44" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+        <v>-0.0483</v>
+      </c>
+      <c r="H44" s="5" t="n">
+        <v>-0.030865</v>
+      </c>
+      <c r="I44" s="5" t="n">
+        <v>-0.038503</v>
       </c>
     </row>
     <row r="45">
       <c r="A45" t="inlineStr">
         <is>
-          <t>income_statement</t>
+          <t>cash_flow</t>
         </is>
       </c>
       <c r="B45" t="inlineStr">
         <is>
-          <t>Shares     Amount         Reserves      Deficit          Total</t>
+          <t>CASH FLOWS FROM FINANCING ACTIVITIES</t>
         </is>
       </c>
       <c r="C45" t="inlineStr">
         <is>
-          <t>Balance, July 31, 2023 5,150,000 427,079 47,333 (137,021)</t>
-        </is>
-      </c>
-      <c r="D45" t="inlineStr"/>
+          <t>Cash, beginning of year</t>
+        </is>
+      </c>
+      <c r="D45" t="inlineStr">
+        <is>
+          <t>BeginningCashPosition</t>
+        </is>
+      </c>
       <c r="E45" t="inlineStr">
         <is>
           <t>-</t>
         </is>
       </c>
-      <c r="F45" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="F45" s="5" t="n">
+        <v>0.213227</v>
       </c>
       <c r="G45" s="5" t="n">
-        <v>0.337391</v>
-      </c>
-      <c r="H45" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="I45" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+        <v>0.399712</v>
+      </c>
+      <c r="H45" s="5" t="n">
+        <v>0.351412</v>
+      </c>
+      <c r="I45" s="5" t="n">
+        <v>0.320547</v>
       </c>
     </row>
     <row r="46">
       <c r="A46" t="inlineStr">
         <is>
-          <t>income_statement</t>
+          <t>cash_flow</t>
         </is>
       </c>
       <c r="B46" t="inlineStr">
         <is>
-          <t>Shares     Amount         Reserves      Deficit          Total</t>
+          <t>CASH FLOWS FROM FINANCING ACTIVITIES</t>
         </is>
       </c>
       <c r="C46" t="inlineStr">
         <is>
-          <t>Exercise of warrants 100,000 24,402 (9,402) -</t>
-        </is>
-      </c>
-      <c r="D46" t="inlineStr"/>
+          <t>Cash, end of year</t>
+        </is>
+      </c>
+      <c r="D46" t="inlineStr">
+        <is>
+          <t>EndCashPosition</t>
+        </is>
+      </c>
       <c r="E46" t="inlineStr">
         <is>
           <t>-</t>
         </is>
       </c>
-      <c r="F46" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="F46" s="5" t="n">
+        <v>0.399712</v>
       </c>
       <c r="G46" s="5" t="n">
-        <v>0.015</v>
-      </c>
-      <c r="H46" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="I46" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+        <v>0.351412</v>
+      </c>
+      <c r="H46" s="5" t="n">
+        <v>0.320547</v>
+      </c>
+      <c r="I46" s="5" t="n">
+        <v>0.282044</v>
       </c>
     </row>
     <row r="47">
       <c r="A47" t="inlineStr">
         <is>
-          <t>income_statement</t>
+          <t>cash_flow</t>
         </is>
       </c>
       <c r="B47" t="inlineStr">
         <is>
-          <t>Shares     Amount         Reserves      Deficit          Total</t>
+          <t>Non-cash investing and financing activities</t>
         </is>
       </c>
       <c r="C47" t="inlineStr">
         <is>
-          <t>Loss for the year - - - (45,556)</t>
+          <t>In addition to cash proceeds of $15,000, share capital includes a $9,402 non-cash transfer from equity reserves, being the grant-date fair value of 100,000 warrants exercised in year ended July</t>
         </is>
       </c>
       <c r="D47" t="inlineStr"/>
@@ -5968,48 +5874,46 @@
         </is>
       </c>
       <c r="G47" s="5" t="n">
-        <v>-0.045556</v>
-      </c>
-      <c r="H47" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="I47" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+        <v>0.002024</v>
+      </c>
+      <c r="H47" s="5" t="n">
+        <v>0.002024</v>
+      </c>
+      <c r="I47" s="5" t="n">
+        <v>3.1e-05</v>
       </c>
     </row>
     <row r="48">
       <c r="A48" t="inlineStr">
         <is>
-          <t>income_statement</t>
+          <t>cash_flow</t>
         </is>
       </c>
       <c r="B48" t="inlineStr">
         <is>
-          <t>Shares     Amount         Reserves      Deficit          Total</t>
+          <t>CASH FLOWS FROM OPERATING ACTIVITIES</t>
         </is>
       </c>
       <c r="C48" t="inlineStr">
         <is>
-          <t>Balance, July 31, 2024 5,250,000 451,481 37,931 (182,577)</t>
-        </is>
-      </c>
-      <c r="D48" t="inlineStr"/>
+          <t>Net loss for the year</t>
+        </is>
+      </c>
+      <c r="D48" t="inlineStr">
+        <is>
+          <t>NetIncomeFromContinuingOperations</t>
+        </is>
+      </c>
       <c r="E48" t="inlineStr">
         <is>
           <t>-</t>
         </is>
       </c>
-      <c r="F48" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="F48" s="5" t="n">
+        <v>-0.077373</v>
       </c>
       <c r="G48" s="5" t="n">
-        <v>0.306835</v>
+        <v>-0.0513</v>
       </c>
       <c r="H48" t="inlineStr">
         <is>
@@ -6025,32 +5929,36 @@
     <row r="49">
       <c r="A49" t="inlineStr">
         <is>
-          <t>income_statement</t>
+          <t>cash_flow</t>
         </is>
       </c>
       <c r="B49" t="inlineStr">
         <is>
-          <t>Shares     Amount         Reserves      Deficit          Total</t>
+          <t>Non-cash expenses</t>
         </is>
       </c>
       <c r="C49" t="inlineStr">
         <is>
-          <t>Loss for the year - - - (38,502)</t>
-        </is>
-      </c>
-      <c r="D49" t="inlineStr"/>
+          <t>Share-based compensation</t>
+        </is>
+      </c>
+      <c r="D49" t="inlineStr">
+        <is>
+          <t>StockBasedCompensation</t>
+        </is>
+      </c>
       <c r="E49" t="inlineStr">
         <is>
           <t>-</t>
         </is>
       </c>
-      <c r="F49" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="G49" s="5" t="n">
-        <v>-0.038502</v>
+      <c r="F49" s="5" t="n">
+        <v>0.037931</v>
+      </c>
+      <c r="G49" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="H49" t="inlineStr">
         <is>
@@ -6066,32 +5974,36 @@
     <row r="50">
       <c r="A50" t="inlineStr">
         <is>
-          <t>income_statement</t>
+          <t>cash_flow</t>
         </is>
       </c>
       <c r="B50" t="inlineStr">
         <is>
-          <t>Shares     Amount         Reserves      Deficit          Total</t>
+          <t>CASH FLOWS FROM FINANCING ACTIVITIES</t>
         </is>
       </c>
       <c r="C50" t="inlineStr">
         <is>
-          <t>Balance, July 31, 2025 5,250,000 451,481 37,931 (221,079)</t>
-        </is>
-      </c>
-      <c r="D50" t="inlineStr"/>
+          <t>Proceeds from sale of shares</t>
+        </is>
+      </c>
+      <c r="D50" t="inlineStr">
+        <is>
+          <t>CommonStockIssuance</t>
+        </is>
+      </c>
       <c r="E50" t="inlineStr">
         <is>
           <t>-</t>
         </is>
       </c>
-      <c r="F50" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="G50" s="5" t="n">
-        <v>0.268333</v>
+      <c r="F50" s="5" t="n">
+        <v>0.3225</v>
+      </c>
+      <c r="G50" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="H50" t="inlineStr">
         <is>
@@ -6107,22 +6019,22 @@
     <row r="51">
       <c r="A51" t="inlineStr">
         <is>
-          <t>income_statement</t>
+          <t>cash_flow</t>
         </is>
       </c>
       <c r="B51" t="inlineStr">
         <is>
-          <t>Transfer agent, shareholder communications, listing and</t>
+          <t>CASH FLOWS FROM FINANCING ACTIVITIES</t>
         </is>
       </c>
       <c r="C51" t="inlineStr">
         <is>
-          <t>Transfer agent, shareholder communications, listing and filing fees 15,965</t>
+          <t>Payments for share issuance costs</t>
         </is>
       </c>
       <c r="D51" t="inlineStr">
         <is>
-          <t>OtherOperatingExpenses</t>
+          <t>NetOtherFinancingCharges</t>
         </is>
       </c>
       <c r="E51" t="inlineStr">
@@ -6131,7 +6043,7 @@
         </is>
       </c>
       <c r="F51" s="5" t="n">
-        <v>0.016361</v>
+        <v>-0.102019</v>
       </c>
       <c r="G51" t="inlineStr">
         <is>
@@ -6152,36 +6064,30 @@
     <row r="52">
       <c r="A52" t="inlineStr">
         <is>
-          <t>income_statement</t>
+          <t>cash_flow</t>
         </is>
       </c>
       <c r="B52" t="inlineStr">
         <is>
-          <t>Transfer agent, shareholder communications, listing and</t>
+          <t>Non-cash investing and financing activities</t>
         </is>
       </c>
       <c r="C52" t="inlineStr">
         <is>
-          <t>Professional fees 11,124</t>
-        </is>
-      </c>
-      <c r="D52" t="inlineStr">
-        <is>
-          <t>ProfessionalExpenseAndContractServicesExpense</t>
-        </is>
-      </c>
+          <t>non-cash costs for the fair value of warrants issued in connection with the Company’s initial public offering and $111,019 in cash costs of which $9,000 was paid in the period from incorporation on March 3, 2021 to July</t>
+        </is>
+      </c>
+      <c r="D52" t="inlineStr"/>
       <c r="E52" t="inlineStr">
         <is>
           <t>-</t>
         </is>
       </c>
       <c r="F52" s="5" t="n">
-        <v>0.015967</v>
-      </c>
-      <c r="G52" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+        <v>0.002021</v>
+      </c>
+      <c r="G52" s="5" t="n">
+        <v>3.1e-05</v>
       </c>
       <c r="H52" t="inlineStr">
         <is>
@@ -6197,31 +6103,27 @@
     <row r="53">
       <c r="A53" t="inlineStr">
         <is>
-          <t>income_statement</t>
+          <t>cash_flow</t>
         </is>
       </c>
       <c r="B53" t="inlineStr">
         <is>
-          <t>Transfer agent, shareholder communications, listing and</t>
+          <t>CASH FLOWS FROM OPERATING ACTIVITIES</t>
         </is>
       </c>
       <c r="C53" t="inlineStr">
         <is>
-          <t>Bank charges 72</t>
-        </is>
-      </c>
-      <c r="D53" t="inlineStr">
-        <is>
-          <t>SellingGeneralAndAdministration</t>
-        </is>
-      </c>
-      <c r="E53" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="F53" s="5" t="n">
-        <v>7.2e-05</v>
+          <t>Net loss for the period (77,373)</t>
+        </is>
+      </c>
+      <c r="D53" t="inlineStr"/>
+      <c r="E53" s="5" t="n">
+        <v>-0.008348</v>
+      </c>
+      <c r="F53" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="G53" t="inlineStr">
         <is>
@@ -6242,20 +6144,24 @@
     <row r="54">
       <c r="A54" t="inlineStr">
         <is>
-          <t>income_statement</t>
+          <t>cash_flow</t>
         </is>
       </c>
       <c r="B54" t="inlineStr">
         <is>
-          <t>Transfer agent, shareholder communications, listing and</t>
+          <t>Non-cash expenses</t>
         </is>
       </c>
       <c r="C54" t="inlineStr">
         <is>
-          <t>Interest income (505)</t>
-        </is>
-      </c>
-      <c r="D54" t="inlineStr"/>
+          <t>Share-based compensation 37,931</t>
+        </is>
+      </c>
+      <c r="D54" t="inlineStr">
+        <is>
+          <t>StockBasedCompensation</t>
+        </is>
+      </c>
       <c r="E54" t="inlineStr">
         <is>
           <t>-</t>
@@ -6285,31 +6191,31 @@
     <row r="55">
       <c r="A55" t="inlineStr">
         <is>
-          <t>income_statement</t>
+          <t>cash_flow</t>
         </is>
       </c>
       <c r="B55" t="inlineStr">
         <is>
-          <t>Transfer agent, shareholder communications, listing and</t>
+          <t>Changes in non-cash working capital items</t>
         </is>
       </c>
       <c r="C55" t="inlineStr">
         <is>
-          <t>Loss and comprehensive loss for the year (45,556)</t>
+          <t>Accounts payable and accrued liabilities 5,446</t>
         </is>
       </c>
       <c r="D55" t="inlineStr">
         <is>
-          <t>NetIncome</t>
-        </is>
-      </c>
-      <c r="E55" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="F55" s="5" t="n">
-        <v>-0.0513</v>
+          <t>ChangeInPayablesAndAccruedExpense</t>
+        </is>
+      </c>
+      <c r="E55" s="5" t="n">
+        <v>0.005575</v>
+      </c>
+      <c r="F55" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="G55" t="inlineStr">
         <is>
@@ -6330,27 +6236,31 @@
     <row r="56">
       <c r="A56" t="inlineStr">
         <is>
-          <t>income_statement</t>
+          <t>cash_flow</t>
         </is>
       </c>
       <c r="B56" t="inlineStr">
         <is>
-          <t>Shares     Amount        Reserves      Deficit          Total</t>
+          <t>Changes in non-cash working capital items</t>
         </is>
       </c>
       <c r="C56" t="inlineStr">
         <is>
-          <t>Balance, July 31, 2022 5,150,000 427,079 47,333 (85,721)</t>
-        </is>
-      </c>
-      <c r="D56" t="inlineStr"/>
-      <c r="E56" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="F56" s="5" t="n">
-        <v>0.388691</v>
+          <t>Net cash used in operating activities (33,996)</t>
+        </is>
+      </c>
+      <c r="D56" t="inlineStr">
+        <is>
+          <t>OperatingCashFlow</t>
+        </is>
+      </c>
+      <c r="E56" s="5" t="n">
+        <v>-0.002773</v>
+      </c>
+      <c r="F56" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="G56" t="inlineStr">
         <is>
@@ -6371,27 +6281,31 @@
     <row r="57">
       <c r="A57" t="inlineStr">
         <is>
-          <t>income_statement</t>
+          <t>cash_flow</t>
         </is>
       </c>
       <c r="B57" t="inlineStr">
         <is>
-          <t>Shares     Amount        Reserves      Deficit          Total</t>
+          <t>CASH FLOWS FROM FINANCING ACTIVITIES</t>
         </is>
       </c>
       <c r="C57" t="inlineStr">
         <is>
-          <t>Loss for the year - - - (51,300)</t>
-        </is>
-      </c>
-      <c r="D57" t="inlineStr"/>
-      <c r="E57" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="F57" s="5" t="n">
-        <v>-0.0513</v>
+          <t>Proceeds from sale of shares 322,500</t>
+        </is>
+      </c>
+      <c r="D57" t="inlineStr">
+        <is>
+          <t>CommonStockIssuance</t>
+        </is>
+      </c>
+      <c r="E57" s="5" t="n">
+        <v>0.225</v>
+      </c>
+      <c r="F57" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="G57" t="inlineStr">
         <is>
@@ -6412,27 +6326,27 @@
     <row r="58">
       <c r="A58" t="inlineStr">
         <is>
-          <t>income_statement</t>
+          <t>cash_flow</t>
         </is>
       </c>
       <c r="B58" t="inlineStr">
         <is>
-          <t>Shares     Amount        Reserves      Deficit          Total</t>
+          <t>CASH FLOWS FROM FINANCING ACTIVITIES</t>
         </is>
       </c>
       <c r="C58" t="inlineStr">
         <is>
-          <t>Balance, July 31, 2023 5,150,000 427,079 47,333 (137,021)</t>
+          <t>Payments for share issuance costs (102,019)</t>
         </is>
       </c>
       <c r="D58" t="inlineStr"/>
-      <c r="E58" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="F58" s="5" t="n">
-        <v>0.337391</v>
+      <c r="E58" s="5" t="n">
+        <v>-0.008999999999999999</v>
+      </c>
+      <c r="F58" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="G58" t="inlineStr">
         <is>
@@ -6453,27 +6367,31 @@
     <row r="59">
       <c r="A59" t="inlineStr">
         <is>
-          <t>income_statement</t>
+          <t>cash_flow</t>
         </is>
       </c>
       <c r="B59" t="inlineStr">
         <is>
-          <t>Shares     Amount        Reserves      Deficit          Total</t>
+          <t>CASH FLOWS FROM FINANCING ACTIVITIES</t>
         </is>
       </c>
       <c r="C59" t="inlineStr">
         <is>
-          <t>Exercise of warrants 100,000 24,402 (9,402) -</t>
-        </is>
-      </c>
-      <c r="D59" t="inlineStr"/>
-      <c r="E59" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="F59" s="5" t="n">
-        <v>0.015</v>
+          <t>Net cash provided by financing activities 220,481</t>
+        </is>
+      </c>
+      <c r="D59" t="inlineStr">
+        <is>
+          <t>FinancingCashFlow</t>
+        </is>
+      </c>
+      <c r="E59" s="5" t="n">
+        <v>0.216</v>
+      </c>
+      <c r="F59" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="G59" t="inlineStr">
         <is>
@@ -6494,27 +6412,31 @@
     <row r="60">
       <c r="A60" t="inlineStr">
         <is>
-          <t>income_statement</t>
+          <t>cash_flow</t>
         </is>
       </c>
       <c r="B60" t="inlineStr">
         <is>
-          <t>Shares     Amount        Reserves      Deficit          Total</t>
+          <t>CASH FLOWS FROM FINANCING ACTIVITIES</t>
         </is>
       </c>
       <c r="C60" t="inlineStr">
         <is>
-          <t>Loss for the year - - - (45,556)</t>
-        </is>
-      </c>
-      <c r="D60" t="inlineStr"/>
-      <c r="E60" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="F60" s="5" t="n">
-        <v>-0.045556</v>
+          <t>Change in cash during the period 186,485</t>
+        </is>
+      </c>
+      <c r="D60" t="inlineStr">
+        <is>
+          <t>ChangesInCash</t>
+        </is>
+      </c>
+      <c r="E60" s="5" t="n">
+        <v>0.213227</v>
+      </c>
+      <c r="F60" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="G60" t="inlineStr">
         <is>
@@ -6535,27 +6457,33 @@
     <row r="61">
       <c r="A61" t="inlineStr">
         <is>
-          <t>income_statement</t>
+          <t>cash_flow</t>
         </is>
       </c>
       <c r="B61" t="inlineStr">
         <is>
-          <t>Shares     Amount        Reserves      Deficit          Total</t>
+          <t>CASH FLOWS FROM FINANCING ACTIVITIES</t>
         </is>
       </c>
       <c r="C61" t="inlineStr">
         <is>
-          <t>Balance, July 31, 2024 5,250,000 451,481 37,931 (182,577)</t>
-        </is>
-      </c>
-      <c r="D61" t="inlineStr"/>
+          <t>Cash, beginning of period 213,227</t>
+        </is>
+      </c>
+      <c r="D61" t="inlineStr">
+        <is>
+          <t>BeginningCashPosition</t>
+        </is>
+      </c>
       <c r="E61" t="inlineStr">
         <is>
           <t>-</t>
         </is>
       </c>
-      <c r="F61" s="5" t="n">
-        <v>0.306835</v>
+      <c r="F61" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="G61" t="inlineStr">
         <is>
@@ -6576,30 +6504,36 @@
     <row r="62">
       <c r="A62" t="inlineStr">
         <is>
-          <t>income_statement</t>
+          <t>cash_flow</t>
         </is>
       </c>
       <c r="B62" t="inlineStr">
         <is>
-          <t>EXPENSES</t>
+          <t>CASH FLOWS FROM FINANCING ACTIVITIES</t>
         </is>
       </c>
       <c r="C62" t="inlineStr">
         <is>
-          <t>Administrative and corporate services (Note 6)</t>
-        </is>
-      </c>
-      <c r="D62" t="inlineStr"/>
-      <c r="E62" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="F62" s="5" t="n">
-        <v>0.0189</v>
-      </c>
-      <c r="G62" s="5" t="n">
-        <v>0.0189</v>
+          <t>Cash, end of period 399,712</t>
+        </is>
+      </c>
+      <c r="D62" t="inlineStr">
+        <is>
+          <t>EndCashPosition</t>
+        </is>
+      </c>
+      <c r="E62" s="5" t="n">
+        <v>0.213227</v>
+      </c>
+      <c r="F62" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="G62" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="H62" t="inlineStr">
         <is>
@@ -6615,34 +6549,32 @@
     <row r="63">
       <c r="A63" t="inlineStr">
         <is>
-          <t>income_statement</t>
+          <t>cash_flow</t>
         </is>
       </c>
       <c r="B63" t="inlineStr">
         <is>
-          <t>Transfer agent, shareholder communications, listing and</t>
+          <t>Non-cash investing and financing activities</t>
         </is>
       </c>
       <c r="C63" t="inlineStr">
         <is>
-          <t>Transfer agent, shareholder communications, listing and filing fees</t>
-        </is>
-      </c>
-      <c r="D63" t="inlineStr">
-        <is>
-          <t>OtherOperatingExpenses</t>
-        </is>
-      </c>
-      <c r="E63" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="F63" s="5" t="n">
-        <v>0.01147</v>
-      </c>
-      <c r="G63" s="5" t="n">
-        <v>0.016361</v>
+          <t>A total of $120,421 was recognized for share issuance costs in the year ended July 31, 2022. This amount includes</t>
+        </is>
+      </c>
+      <c r="D63" t="inlineStr"/>
+      <c r="E63" s="5" t="n">
+        <v>0.009402000000000001</v>
+      </c>
+      <c r="F63" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="G63" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="H63" t="inlineStr">
         <is>
@@ -6658,34 +6590,32 @@
     <row r="64">
       <c r="A64" t="inlineStr">
         <is>
-          <t>income_statement</t>
+          <t>cash_flow</t>
         </is>
       </c>
       <c r="B64" t="inlineStr">
         <is>
-          <t>Transfer agent, shareholder communications, listing and</t>
+          <t>Non-cash investing and financing activities</t>
         </is>
       </c>
       <c r="C64" t="inlineStr">
         <is>
-          <t>Professional fees</t>
-        </is>
-      </c>
-      <c r="D64" t="inlineStr">
-        <is>
-          <t>ProfessionalExpenseAndContractServicesExpense</t>
-        </is>
-      </c>
-      <c r="E64" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="F64" s="5" t="n">
-        <v>0.008999999999999999</v>
-      </c>
-      <c r="G64" s="5" t="n">
-        <v>0.015967</v>
+          <t>non-cash costs for the fair value of warrants issued in connection with the Company’s initial public offering and</t>
+        </is>
+      </c>
+      <c r="D64" t="inlineStr"/>
+      <c r="E64" s="5" t="n">
+        <v>0.111019</v>
+      </c>
+      <c r="F64" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="G64" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="H64" t="inlineStr">
         <is>
@@ -6704,14 +6634,10 @@
           <t>income_statement</t>
         </is>
       </c>
-      <c r="B65" t="inlineStr">
-        <is>
-          <t>Transfer agent, shareholder communications, listing and</t>
-        </is>
-      </c>
+      <c r="B65" t="inlineStr"/>
       <c r="C65" t="inlineStr">
         <is>
-          <t>Office and sundry</t>
+          <t>FOR THE YEARS ENDED JULY</t>
         </is>
       </c>
       <c r="D65" t="inlineStr"/>
@@ -6721,10 +6647,10 @@
         </is>
       </c>
       <c r="F65" s="5" t="n">
-        <v>7.2e-05</v>
+        <v>3.1e-05</v>
       </c>
       <c r="G65" s="5" t="n">
-        <v>7.2e-05</v>
+        <v>3.1e-05</v>
       </c>
       <c r="H65" t="inlineStr">
         <is>
@@ -6745,27 +6671,23 @@
       </c>
       <c r="B66" t="inlineStr">
         <is>
-          <t>Transfer agent, shareholder communications, listing and</t>
+          <t>EXPENSES</t>
         </is>
       </c>
       <c r="C66" t="inlineStr">
         <is>
-          <t>Share-based compensation (Notes 5 and 6)</t>
+          <t>Administrative and corporate services (Note 6) 18,900</t>
         </is>
       </c>
       <c r="D66" t="inlineStr"/>
-      <c r="E66" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="E66" s="5" t="n">
+        <v>0.002835</v>
       </c>
       <c r="F66" s="5" t="n">
-        <v>0.037931</v>
-      </c>
-      <c r="G66" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+        <v>0.0189</v>
+      </c>
+      <c r="G66" s="5" t="n">
+        <v>0.0189</v>
       </c>
       <c r="H66" t="inlineStr">
         <is>
@@ -6791,12 +6713,12 @@
       </c>
       <c r="C67" t="inlineStr">
         <is>
-          <t>Loss and comprehensive loss for the year</t>
+          <t>Transfer agent, shareholder communications, listing and filing fees 15,789</t>
         </is>
       </c>
       <c r="D67" t="inlineStr">
         <is>
-          <t>NetIncome</t>
+          <t>OtherOperatingExpenses</t>
         </is>
       </c>
       <c r="E67" t="inlineStr">
@@ -6804,11 +6726,13 @@
           <t>-</t>
         </is>
       </c>
-      <c r="F67" s="5" t="n">
-        <v>-0.077373</v>
+      <c r="F67" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="G67" s="5" t="n">
-        <v>-0.0513</v>
+        <v>0.015965</v>
       </c>
       <c r="H67" t="inlineStr">
         <is>
@@ -6834,12 +6758,12 @@
       </c>
       <c r="C68" t="inlineStr">
         <is>
-          <t>Basic and diluted loss per common share (Note 5)</t>
+          <t>Professional fees 11,451</t>
         </is>
       </c>
       <c r="D68" t="inlineStr">
         <is>
-          <t>BasicEPS</t>
+          <t>ProfessionalExpenseAndContractServicesExpense</t>
         </is>
       </c>
       <c r="E68" t="inlineStr">
@@ -6847,11 +6771,13 @@
           <t>-</t>
         </is>
       </c>
-      <c r="F68" s="5" t="n">
-        <v>-2e-08</v>
+      <c r="F68" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="G68" s="5" t="n">
-        <v>-1e-08</v>
+        <v>0.011124</v>
       </c>
       <c r="H68" t="inlineStr">
         <is>
@@ -6872,25 +6798,31 @@
       </c>
       <c r="B69" t="inlineStr">
         <is>
-          <t>Shares     Amount         Reserves      Deficit          Total</t>
+          <t>Transfer agent, shareholder communications, listing and</t>
         </is>
       </c>
       <c r="C69" t="inlineStr">
         <is>
-          <t>Balance, July 31, 2021 3,000,000 225,000 -</t>
-        </is>
-      </c>
-      <c r="D69" t="inlineStr"/>
+          <t>Bank charges 75</t>
+        </is>
+      </c>
+      <c r="D69" t="inlineStr">
+        <is>
+          <t>SellingGeneralAndAdministration</t>
+        </is>
+      </c>
       <c r="E69" t="inlineStr">
         <is>
           <t>-</t>
         </is>
       </c>
-      <c r="F69" s="5" t="n">
-        <v>0.216652</v>
+      <c r="F69" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="G69" s="5" t="n">
-        <v>-0.008348</v>
+        <v>7.2e-05</v>
       </c>
       <c r="H69" t="inlineStr">
         <is>
@@ -6911,12 +6843,12 @@
       </c>
       <c r="B70" t="inlineStr">
         <is>
-          <t>Shares     Amount         Reserves      Deficit          Total</t>
+          <t>Transfer agent, shareholder communications, listing and</t>
         </is>
       </c>
       <c r="C70" t="inlineStr">
         <is>
-          <t>Shares issued 2,150,000 322,500 -</t>
+          <t>Interest income (7,713)</t>
         </is>
       </c>
       <c r="D70" t="inlineStr"/>
@@ -6925,13 +6857,13 @@
           <t>-</t>
         </is>
       </c>
-      <c r="F70" s="5" t="n">
-        <v>0.3225</v>
-      </c>
-      <c r="G70" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="F70" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="G70" s="5" t="n">
+        <v>-0.000505</v>
       </c>
       <c r="H70" t="inlineStr">
         <is>
@@ -6952,27 +6884,31 @@
       </c>
       <c r="B71" t="inlineStr">
         <is>
-          <t>Shares     Amount         Reserves      Deficit          Total</t>
+          <t>Transfer agent, shareholder communications, listing and</t>
         </is>
       </c>
       <c r="C71" t="inlineStr">
         <is>
-          <t>Share issuance costs - (120,421) 9,402</t>
-        </is>
-      </c>
-      <c r="D71" t="inlineStr"/>
+          <t>Loss and comprehensive loss for the year (38,502)</t>
+        </is>
+      </c>
+      <c r="D71" t="inlineStr">
+        <is>
+          <t>NetIncome</t>
+        </is>
+      </c>
       <c r="E71" t="inlineStr">
         <is>
           <t>-</t>
         </is>
       </c>
-      <c r="F71" s="5" t="n">
-        <v>-0.111019</v>
-      </c>
-      <c r="G71" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="F71" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="G71" s="5" t="n">
+        <v>-0.045556</v>
       </c>
       <c r="H71" t="inlineStr">
         <is>
@@ -6993,12 +6929,12 @@
       </c>
       <c r="B72" t="inlineStr">
         <is>
-          <t>Shares     Amount         Reserves      Deficit          Total</t>
+          <t>Transfer agent, shareholder communications, listing and</t>
         </is>
       </c>
       <c r="C72" t="inlineStr">
         <is>
-          <t>Share-based compensation - - 37,931</t>
+          <t>Basic and diluted loss per common share (Note 5) (0.01)</t>
         </is>
       </c>
       <c r="D72" t="inlineStr"/>
@@ -7008,12 +6944,10 @@
         </is>
       </c>
       <c r="F72" s="5" t="n">
-        <v>0.037931</v>
-      </c>
-      <c r="G72" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+        <v>-1e-08</v>
+      </c>
+      <c r="G72" s="5" t="n">
+        <v>-1e-08</v>
       </c>
       <c r="H72" t="inlineStr">
         <is>
@@ -7039,24 +6973,22 @@
       </c>
       <c r="C73" t="inlineStr">
         <is>
-          <t>Loss for the year - - -</t>
-        </is>
-      </c>
-      <c r="D73" t="inlineStr">
-        <is>
-          <t>NetIncome</t>
-        </is>
-      </c>
+          <t>Balance, July 31, 2023 5,150,000 427,079 47,333 (137,021)</t>
+        </is>
+      </c>
+      <c r="D73" t="inlineStr"/>
       <c r="E73" t="inlineStr">
         <is>
           <t>-</t>
         </is>
       </c>
-      <c r="F73" s="5" t="n">
-        <v>-0.077373</v>
+      <c r="F73" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="G73" s="5" t="n">
-        <v>-0.077373</v>
+        <v>0.337391</v>
       </c>
       <c r="H73" t="inlineStr">
         <is>
@@ -7082,7 +7014,7 @@
       </c>
       <c r="C74" t="inlineStr">
         <is>
-          <t>Balance, July 31, 2022 5,150,000 427,079 47,333</t>
+          <t>Exercise of warrants 100,000 24,402 (9,402) -</t>
         </is>
       </c>
       <c r="D74" t="inlineStr"/>
@@ -7091,11 +7023,13 @@
           <t>-</t>
         </is>
       </c>
-      <c r="F74" s="5" t="n">
-        <v>0.388691</v>
+      <c r="F74" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="G74" s="5" t="n">
-        <v>-0.08572100000000001</v>
+        <v>0.015</v>
       </c>
       <c r="H74" t="inlineStr">
         <is>
@@ -7121,7 +7055,7 @@
       </c>
       <c r="C75" t="inlineStr">
         <is>
-          <t>Balance, July 31, 2023 5,150,000 427,079 47,333</t>
+          <t>Loss for the year - - - (45,556)</t>
         </is>
       </c>
       <c r="D75" t="inlineStr"/>
@@ -7130,11 +7064,13 @@
           <t>-</t>
         </is>
       </c>
-      <c r="F75" s="5" t="n">
-        <v>0.337391</v>
+      <c r="F75" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="G75" s="5" t="n">
-        <v>-0.137021</v>
+        <v>-0.045556</v>
       </c>
       <c r="H75" t="inlineStr">
         <is>
@@ -7155,12 +7091,12 @@
       </c>
       <c r="B76" t="inlineStr">
         <is>
-          <t>EXPENSES</t>
+          <t>Shares     Amount         Reserves      Deficit          Total</t>
         </is>
       </c>
       <c r="C76" t="inlineStr">
         <is>
-          <t>Share-based compensation (Notes 5 and 6) 37,931</t>
+          <t>Balance, July 31, 2024 5,250,000 451,481 37,931 (182,577)</t>
         </is>
       </c>
       <c r="D76" t="inlineStr"/>
@@ -7174,10 +7110,8 @@
           <t>-</t>
         </is>
       </c>
-      <c r="G76" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="G76" s="5" t="n">
+        <v>0.306835</v>
       </c>
       <c r="H76" t="inlineStr">
         <is>
@@ -7198,19 +7132,15 @@
       </c>
       <c r="B77" t="inlineStr">
         <is>
-          <t>Transfer  agent, shareholder communications,  listing and</t>
+          <t>Shares     Amount         Reserves      Deficit          Total</t>
         </is>
       </c>
       <c r="C77" t="inlineStr">
         <is>
-          <t>Transfer  agent, shareholder communications,  listing and filing fees 11,470</t>
-        </is>
-      </c>
-      <c r="D77" t="inlineStr">
-        <is>
-          <t>OtherOperatingExpenses</t>
-        </is>
-      </c>
+          <t>Loss for the year - - - (38,502)</t>
+        </is>
+      </c>
+      <c r="D77" t="inlineStr"/>
       <c r="E77" t="inlineStr">
         <is>
           <t>-</t>
@@ -7221,10 +7151,8 @@
           <t>-</t>
         </is>
       </c>
-      <c r="G77" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="G77" s="5" t="n">
+        <v>-0.038502</v>
       </c>
       <c r="H77" t="inlineStr">
         <is>
@@ -7245,31 +7173,27 @@
       </c>
       <c r="B78" t="inlineStr">
         <is>
-          <t>Transfer  agent, shareholder communications,  listing and</t>
+          <t>Shares     Amount         Reserves      Deficit          Total</t>
         </is>
       </c>
       <c r="C78" t="inlineStr">
         <is>
-          <t>Professional fees 9,000</t>
-        </is>
-      </c>
-      <c r="D78" t="inlineStr">
-        <is>
-          <t>ProfessionalExpenseAndContractServicesExpense</t>
-        </is>
-      </c>
-      <c r="E78" s="5" t="n">
-        <v>0.005501</v>
+          <t>Balance, July 31, 2025 5,250,000 451,481 37,931 (221,079)</t>
+        </is>
+      </c>
+      <c r="D78" t="inlineStr"/>
+      <c r="E78" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="F78" t="inlineStr">
         <is>
           <t>-</t>
         </is>
       </c>
-      <c r="G78" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="G78" s="5" t="n">
+        <v>0.268333</v>
       </c>
       <c r="H78" t="inlineStr">
         <is>
@@ -7290,22 +7214,26 @@
       </c>
       <c r="B79" t="inlineStr">
         <is>
-          <t>Transfer  agent, shareholder communications,  listing and</t>
+          <t>Transfer agent, shareholder communications, listing and</t>
         </is>
       </c>
       <c r="C79" t="inlineStr">
         <is>
-          <t>Office and sundry 72</t>
-        </is>
-      </c>
-      <c r="D79" t="inlineStr"/>
-      <c r="E79" s="5" t="n">
-        <v>1.2e-05</v>
-      </c>
-      <c r="F79" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+          <t>Transfer agent, shareholder communications, listing and filing fees 15,965</t>
+        </is>
+      </c>
+      <c r="D79" t="inlineStr">
+        <is>
+          <t>OtherOperatingExpenses</t>
+        </is>
+      </c>
+      <c r="E79" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="F79" s="5" t="n">
+        <v>0.016361</v>
       </c>
       <c r="G79" t="inlineStr">
         <is>
@@ -7331,22 +7259,26 @@
       </c>
       <c r="B80" t="inlineStr">
         <is>
-          <t>Transfer  agent, shareholder communications,  listing and</t>
+          <t>Transfer agent, shareholder communications, listing and</t>
         </is>
       </c>
       <c r="C80" t="inlineStr">
         <is>
-          <t>Loss and comprehensive loss for the period (77,373)</t>
-        </is>
-      </c>
-      <c r="D80" t="inlineStr"/>
-      <c r="E80" s="5" t="n">
-        <v>-0.008348</v>
-      </c>
-      <c r="F80" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+          <t>Professional fees 11,124</t>
+        </is>
+      </c>
+      <c r="D80" t="inlineStr">
+        <is>
+          <t>ProfessionalExpenseAndContractServicesExpense</t>
+        </is>
+      </c>
+      <c r="E80" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="F80" s="5" t="n">
+        <v>0.015967</v>
       </c>
       <c r="G80" t="inlineStr">
         <is>
@@ -7372,22 +7304,26 @@
       </c>
       <c r="B81" t="inlineStr">
         <is>
-          <t>Transfer  agent, shareholder communications,  listing and</t>
+          <t>Transfer agent, shareholder communications, listing and</t>
         </is>
       </c>
       <c r="C81" t="inlineStr">
         <is>
-          <t>Basic and diluted loss per common share (Note 5) (0.02)</t>
-        </is>
-      </c>
-      <c r="D81" t="inlineStr"/>
-      <c r="E81" s="5" t="n">
-        <v>-1e-08</v>
-      </c>
-      <c r="F81" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+          <t>Bank charges 72</t>
+        </is>
+      </c>
+      <c r="D81" t="inlineStr">
+        <is>
+          <t>SellingGeneralAndAdministration</t>
+        </is>
+      </c>
+      <c r="E81" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="F81" s="5" t="n">
+        <v>7.2e-05</v>
       </c>
       <c r="G81" t="inlineStr">
         <is>
@@ -7413,12 +7349,12 @@
       </c>
       <c r="B82" t="inlineStr">
         <is>
-          <t>Shares     Amount         Reserves      Deficit          Total</t>
+          <t>Transfer agent, shareholder communications, listing and</t>
         </is>
       </c>
       <c r="C82" t="inlineStr">
         <is>
-          <t>Balance, March 3, 2021 - - - -</t>
+          <t>Interest income (505)</t>
         </is>
       </c>
       <c r="D82" t="inlineStr"/>
@@ -7456,22 +7392,26 @@
       </c>
       <c r="B83" t="inlineStr">
         <is>
-          <t>Shares     Amount         Reserves      Deficit          Total</t>
+          <t>Transfer agent, shareholder communications, listing and</t>
         </is>
       </c>
       <c r="C83" t="inlineStr">
         <is>
-          <t>Shares issued 3,000,000 225,000 - -</t>
-        </is>
-      </c>
-      <c r="D83" t="inlineStr"/>
-      <c r="E83" s="5" t="n">
-        <v>0.225</v>
-      </c>
-      <c r="F83" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+          <t>Loss and comprehensive loss for the year (45,556)</t>
+        </is>
+      </c>
+      <c r="D83" t="inlineStr">
+        <is>
+          <t>NetIncome</t>
+        </is>
+      </c>
+      <c r="E83" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="F83" s="5" t="n">
+        <v>-0.0513</v>
       </c>
       <c r="G83" t="inlineStr">
         <is>
@@ -7497,22 +7437,22 @@
       </c>
       <c r="B84" t="inlineStr">
         <is>
-          <t>Shares     Amount         Reserves      Deficit          Total</t>
+          <t>Shares     Amount        Reserves      Deficit          Total</t>
         </is>
       </c>
       <c r="C84" t="inlineStr">
         <is>
-          <t>Loss for the period - - - (8,348)</t>
+          <t>Balance, July 31, 2022 5,150,000 427,079 47,333 (85,721)</t>
         </is>
       </c>
       <c r="D84" t="inlineStr"/>
-      <c r="E84" s="5" t="n">
-        <v>-0.008348</v>
-      </c>
-      <c r="F84" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="E84" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="F84" s="5" t="n">
+        <v>0.388691</v>
       </c>
       <c r="G84" t="inlineStr">
         <is>
@@ -7538,22 +7478,22 @@
       </c>
       <c r="B85" t="inlineStr">
         <is>
-          <t>Shares     Amount         Reserves      Deficit          Total</t>
+          <t>Shares     Amount        Reserves      Deficit          Total</t>
         </is>
       </c>
       <c r="C85" t="inlineStr">
         <is>
-          <t>Balance, July 31, 2021 3,000,000 225,000 - (8,348)</t>
+          <t>Loss for the year - - - (51,300)</t>
         </is>
       </c>
       <c r="D85" t="inlineStr"/>
-      <c r="E85" s="5" t="n">
-        <v>0.216652</v>
-      </c>
-      <c r="F85" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="E85" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="F85" s="5" t="n">
+        <v>-0.0513</v>
       </c>
       <c r="G85" t="inlineStr">
         <is>
@@ -7579,22 +7519,22 @@
       </c>
       <c r="B86" t="inlineStr">
         <is>
-          <t>Shares     Amount         Reserves      Deficit          Total</t>
+          <t>Shares     Amount        Reserves      Deficit          Total</t>
         </is>
       </c>
       <c r="C86" t="inlineStr">
         <is>
-          <t>Shares issued 2,150,000 322,500 - -</t>
+          <t>Balance, July 31, 2023 5,150,000 427,079 47,333 (137,021)</t>
         </is>
       </c>
       <c r="D86" t="inlineStr"/>
-      <c r="E86" s="5" t="n">
-        <v>0.3225</v>
-      </c>
-      <c r="F86" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="E86" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="F86" s="5" t="n">
+        <v>0.337391</v>
       </c>
       <c r="G86" t="inlineStr">
         <is>
@@ -7620,22 +7560,22 @@
       </c>
       <c r="B87" t="inlineStr">
         <is>
-          <t>Shares     Amount         Reserves      Deficit          Total</t>
+          <t>Shares     Amount        Reserves      Deficit          Total</t>
         </is>
       </c>
       <c r="C87" t="inlineStr">
         <is>
-          <t>Share issuance costs - (120,421) 9,402 -</t>
+          <t>Exercise of warrants 100,000 24,402 (9,402) -</t>
         </is>
       </c>
       <c r="D87" t="inlineStr"/>
-      <c r="E87" s="5" t="n">
-        <v>-0.111019</v>
-      </c>
-      <c r="F87" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="E87" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="F87" s="5" t="n">
+        <v>0.015</v>
       </c>
       <c r="G87" t="inlineStr">
         <is>
@@ -7661,22 +7601,22 @@
       </c>
       <c r="B88" t="inlineStr">
         <is>
-          <t>Shares     Amount         Reserves      Deficit          Total</t>
+          <t>Shares     Amount        Reserves      Deficit          Total</t>
         </is>
       </c>
       <c r="C88" t="inlineStr">
         <is>
-          <t>Share-based compensation - - 37,931 -</t>
+          <t>Loss for the year - - - (45,556)</t>
         </is>
       </c>
       <c r="D88" t="inlineStr"/>
-      <c r="E88" s="5" t="n">
-        <v>0.037931</v>
-      </c>
-      <c r="F88" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="E88" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="F88" s="5" t="n">
+        <v>-0.045556</v>
       </c>
       <c r="G88" t="inlineStr">
         <is>
@@ -7702,22 +7642,22 @@
       </c>
       <c r="B89" t="inlineStr">
         <is>
-          <t>Shares     Amount         Reserves      Deficit          Total</t>
+          <t>Shares     Amount        Reserves      Deficit          Total</t>
         </is>
       </c>
       <c r="C89" t="inlineStr">
         <is>
-          <t>Loss for the year - - - (77,373)</t>
+          <t>Balance, July 31, 2024 5,250,000 451,481 37,931 (182,577)</t>
         </is>
       </c>
       <c r="D89" t="inlineStr"/>
-      <c r="E89" s="5" t="n">
-        <v>-0.077373</v>
-      </c>
-      <c r="F89" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="E89" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="F89" s="5" t="n">
+        <v>0.306835</v>
       </c>
       <c r="G89" t="inlineStr">
         <is>
@@ -7743,34 +7683,1196 @@
       </c>
       <c r="B90" t="inlineStr">
         <is>
+          <t>EXPENSES</t>
+        </is>
+      </c>
+      <c r="C90" t="inlineStr">
+        <is>
+          <t>Administrative and corporate services (Note 6)</t>
+        </is>
+      </c>
+      <c r="D90" t="inlineStr"/>
+      <c r="E90" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="F90" s="5" t="n">
+        <v>0.0189</v>
+      </c>
+      <c r="G90" s="5" t="n">
+        <v>0.0189</v>
+      </c>
+      <c r="H90" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="I90" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+    </row>
+    <row r="91">
+      <c r="A91" t="inlineStr">
+        <is>
+          <t>income_statement</t>
+        </is>
+      </c>
+      <c r="B91" t="inlineStr">
+        <is>
+          <t>Transfer agent, shareholder communications, listing and</t>
+        </is>
+      </c>
+      <c r="C91" t="inlineStr">
+        <is>
+          <t>Transfer agent, shareholder communications, listing and filing fees</t>
+        </is>
+      </c>
+      <c r="D91" t="inlineStr">
+        <is>
+          <t>OtherOperatingExpenses</t>
+        </is>
+      </c>
+      <c r="E91" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="F91" s="5" t="n">
+        <v>0.01147</v>
+      </c>
+      <c r="G91" s="5" t="n">
+        <v>0.016361</v>
+      </c>
+      <c r="H91" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="I91" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+    </row>
+    <row r="92">
+      <c r="A92" t="inlineStr">
+        <is>
+          <t>income_statement</t>
+        </is>
+      </c>
+      <c r="B92" t="inlineStr">
+        <is>
+          <t>Transfer agent, shareholder communications, listing and</t>
+        </is>
+      </c>
+      <c r="C92" t="inlineStr">
+        <is>
+          <t>Professional fees</t>
+        </is>
+      </c>
+      <c r="D92" t="inlineStr">
+        <is>
+          <t>ProfessionalExpenseAndContractServicesExpense</t>
+        </is>
+      </c>
+      <c r="E92" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="F92" s="5" t="n">
+        <v>0.008999999999999999</v>
+      </c>
+      <c r="G92" s="5" t="n">
+        <v>0.015967</v>
+      </c>
+      <c r="H92" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="I92" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+    </row>
+    <row r="93">
+      <c r="A93" t="inlineStr">
+        <is>
+          <t>income_statement</t>
+        </is>
+      </c>
+      <c r="B93" t="inlineStr">
+        <is>
+          <t>Transfer agent, shareholder communications, listing and</t>
+        </is>
+      </c>
+      <c r="C93" t="inlineStr">
+        <is>
+          <t>Office and sundry</t>
+        </is>
+      </c>
+      <c r="D93" t="inlineStr"/>
+      <c r="E93" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="F93" s="5" t="n">
+        <v>7.2e-05</v>
+      </c>
+      <c r="G93" s="5" t="n">
+        <v>7.2e-05</v>
+      </c>
+      <c r="H93" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="I93" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+    </row>
+    <row r="94">
+      <c r="A94" t="inlineStr">
+        <is>
+          <t>income_statement</t>
+        </is>
+      </c>
+      <c r="B94" t="inlineStr">
+        <is>
+          <t>Transfer agent, shareholder communications, listing and</t>
+        </is>
+      </c>
+      <c r="C94" t="inlineStr">
+        <is>
+          <t>Share-based compensation (Notes 5 and 6)</t>
+        </is>
+      </c>
+      <c r="D94" t="inlineStr"/>
+      <c r="E94" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="F94" s="5" t="n">
+        <v>0.037931</v>
+      </c>
+      <c r="G94" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="H94" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="I94" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+    </row>
+    <row r="95">
+      <c r="A95" t="inlineStr">
+        <is>
+          <t>income_statement</t>
+        </is>
+      </c>
+      <c r="B95" t="inlineStr">
+        <is>
+          <t>Transfer agent, shareholder communications, listing and</t>
+        </is>
+      </c>
+      <c r="C95" t="inlineStr">
+        <is>
+          <t>Loss and comprehensive loss for the year</t>
+        </is>
+      </c>
+      <c r="D95" t="inlineStr">
+        <is>
+          <t>NetIncome</t>
+        </is>
+      </c>
+      <c r="E95" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="F95" s="5" t="n">
+        <v>-0.077373</v>
+      </c>
+      <c r="G95" s="5" t="n">
+        <v>-0.0513</v>
+      </c>
+      <c r="H95" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="I95" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+    </row>
+    <row r="96">
+      <c r="A96" t="inlineStr">
+        <is>
+          <t>income_statement</t>
+        </is>
+      </c>
+      <c r="B96" t="inlineStr">
+        <is>
+          <t>Transfer agent, shareholder communications, listing and</t>
+        </is>
+      </c>
+      <c r="C96" t="inlineStr">
+        <is>
+          <t>Basic and diluted loss per common share (Note 5)</t>
+        </is>
+      </c>
+      <c r="D96" t="inlineStr">
+        <is>
+          <t>BasicEPS</t>
+        </is>
+      </c>
+      <c r="E96" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="F96" s="5" t="n">
+        <v>-2e-08</v>
+      </c>
+      <c r="G96" s="5" t="n">
+        <v>-1e-08</v>
+      </c>
+      <c r="H96" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="I96" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+    </row>
+    <row r="97">
+      <c r="A97" t="inlineStr">
+        <is>
+          <t>income_statement</t>
+        </is>
+      </c>
+      <c r="B97" t="inlineStr">
+        <is>
           <t>Shares     Amount         Reserves      Deficit          Total</t>
         </is>
       </c>
-      <c r="C90" t="inlineStr">
+      <c r="C97" t="inlineStr">
+        <is>
+          <t>Balance, July 31, 2021 3,000,000 225,000 -</t>
+        </is>
+      </c>
+      <c r="D97" t="inlineStr"/>
+      <c r="E97" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="F97" s="5" t="n">
+        <v>0.216652</v>
+      </c>
+      <c r="G97" s="5" t="n">
+        <v>-0.008348</v>
+      </c>
+      <c r="H97" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="I97" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+    </row>
+    <row r="98">
+      <c r="A98" t="inlineStr">
+        <is>
+          <t>income_statement</t>
+        </is>
+      </c>
+      <c r="B98" t="inlineStr">
+        <is>
+          <t>Shares     Amount         Reserves      Deficit          Total</t>
+        </is>
+      </c>
+      <c r="C98" t="inlineStr">
+        <is>
+          <t>Shares issued 2,150,000 322,500 -</t>
+        </is>
+      </c>
+      <c r="D98" t="inlineStr"/>
+      <c r="E98" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="F98" s="5" t="n">
+        <v>0.3225</v>
+      </c>
+      <c r="G98" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="H98" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="I98" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+    </row>
+    <row r="99">
+      <c r="A99" t="inlineStr">
+        <is>
+          <t>income_statement</t>
+        </is>
+      </c>
+      <c r="B99" t="inlineStr">
+        <is>
+          <t>Shares     Amount         Reserves      Deficit          Total</t>
+        </is>
+      </c>
+      <c r="C99" t="inlineStr">
+        <is>
+          <t>Share issuance costs - (120,421) 9,402</t>
+        </is>
+      </c>
+      <c r="D99" t="inlineStr"/>
+      <c r="E99" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="F99" s="5" t="n">
+        <v>-0.111019</v>
+      </c>
+      <c r="G99" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="H99" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="I99" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+    </row>
+    <row r="100">
+      <c r="A100" t="inlineStr">
+        <is>
+          <t>income_statement</t>
+        </is>
+      </c>
+      <c r="B100" t="inlineStr">
+        <is>
+          <t>Shares     Amount         Reserves      Deficit          Total</t>
+        </is>
+      </c>
+      <c r="C100" t="inlineStr">
+        <is>
+          <t>Share-based compensation - - 37,931</t>
+        </is>
+      </c>
+      <c r="D100" t="inlineStr"/>
+      <c r="E100" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="F100" s="5" t="n">
+        <v>0.037931</v>
+      </c>
+      <c r="G100" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="H100" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="I100" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+    </row>
+    <row r="101">
+      <c r="A101" t="inlineStr">
+        <is>
+          <t>income_statement</t>
+        </is>
+      </c>
+      <c r="B101" t="inlineStr">
+        <is>
+          <t>Shares     Amount         Reserves      Deficit          Total</t>
+        </is>
+      </c>
+      <c r="C101" t="inlineStr">
+        <is>
+          <t>Loss for the year - - -</t>
+        </is>
+      </c>
+      <c r="D101" t="inlineStr">
+        <is>
+          <t>NetIncome</t>
+        </is>
+      </c>
+      <c r="E101" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="F101" s="5" t="n">
+        <v>-0.077373</v>
+      </c>
+      <c r="G101" s="5" t="n">
+        <v>-0.077373</v>
+      </c>
+      <c r="H101" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="I101" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+    </row>
+    <row r="102">
+      <c r="A102" t="inlineStr">
+        <is>
+          <t>income_statement</t>
+        </is>
+      </c>
+      <c r="B102" t="inlineStr">
+        <is>
+          <t>Shares     Amount         Reserves      Deficit          Total</t>
+        </is>
+      </c>
+      <c r="C102" t="inlineStr">
+        <is>
+          <t>Balance, July 31, 2022 5,150,000 427,079 47,333</t>
+        </is>
+      </c>
+      <c r="D102" t="inlineStr"/>
+      <c r="E102" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="F102" s="5" t="n">
+        <v>0.388691</v>
+      </c>
+      <c r="G102" s="5" t="n">
+        <v>-0.08572100000000001</v>
+      </c>
+      <c r="H102" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="I102" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+    </row>
+    <row r="103">
+      <c r="A103" t="inlineStr">
+        <is>
+          <t>income_statement</t>
+        </is>
+      </c>
+      <c r="B103" t="inlineStr">
+        <is>
+          <t>Shares     Amount         Reserves      Deficit          Total</t>
+        </is>
+      </c>
+      <c r="C103" t="inlineStr">
+        <is>
+          <t>Balance, July 31, 2023 5,150,000 427,079 47,333</t>
+        </is>
+      </c>
+      <c r="D103" t="inlineStr"/>
+      <c r="E103" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="F103" s="5" t="n">
+        <v>0.337391</v>
+      </c>
+      <c r="G103" s="5" t="n">
+        <v>-0.137021</v>
+      </c>
+      <c r="H103" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="I103" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+    </row>
+    <row r="104">
+      <c r="A104" t="inlineStr">
+        <is>
+          <t>income_statement</t>
+        </is>
+      </c>
+      <c r="B104" t="inlineStr">
+        <is>
+          <t>EXPENSES</t>
+        </is>
+      </c>
+      <c r="C104" t="inlineStr">
+        <is>
+          <t>Share-based compensation (Notes 5 and 6) 37,931</t>
+        </is>
+      </c>
+      <c r="D104" t="inlineStr"/>
+      <c r="E104" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="F104" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="G104" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="H104" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="I104" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+    </row>
+    <row r="105">
+      <c r="A105" t="inlineStr">
+        <is>
+          <t>income_statement</t>
+        </is>
+      </c>
+      <c r="B105" t="inlineStr">
+        <is>
+          <t>Transfer  agent, shareholder communications,  listing and</t>
+        </is>
+      </c>
+      <c r="C105" t="inlineStr">
+        <is>
+          <t>Transfer  agent, shareholder communications,  listing and filing fees 11,470</t>
+        </is>
+      </c>
+      <c r="D105" t="inlineStr">
+        <is>
+          <t>OtherOperatingExpenses</t>
+        </is>
+      </c>
+      <c r="E105" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="F105" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="G105" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="H105" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="I105" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+    </row>
+    <row r="106">
+      <c r="A106" t="inlineStr">
+        <is>
+          <t>income_statement</t>
+        </is>
+      </c>
+      <c r="B106" t="inlineStr">
+        <is>
+          <t>Transfer  agent, shareholder communications,  listing and</t>
+        </is>
+      </c>
+      <c r="C106" t="inlineStr">
+        <is>
+          <t>Professional fees 9,000</t>
+        </is>
+      </c>
+      <c r="D106" t="inlineStr">
+        <is>
+          <t>ProfessionalExpenseAndContractServicesExpense</t>
+        </is>
+      </c>
+      <c r="E106" s="5" t="n">
+        <v>0.005501</v>
+      </c>
+      <c r="F106" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="G106" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="H106" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="I106" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+    </row>
+    <row r="107">
+      <c r="A107" t="inlineStr">
+        <is>
+          <t>income_statement</t>
+        </is>
+      </c>
+      <c r="B107" t="inlineStr">
+        <is>
+          <t>Transfer  agent, shareholder communications,  listing and</t>
+        </is>
+      </c>
+      <c r="C107" t="inlineStr">
+        <is>
+          <t>Office and sundry 72</t>
+        </is>
+      </c>
+      <c r="D107" t="inlineStr"/>
+      <c r="E107" s="5" t="n">
+        <v>1.2e-05</v>
+      </c>
+      <c r="F107" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="G107" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="H107" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="I107" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+    </row>
+    <row r="108">
+      <c r="A108" t="inlineStr">
+        <is>
+          <t>income_statement</t>
+        </is>
+      </c>
+      <c r="B108" t="inlineStr">
+        <is>
+          <t>Transfer  agent, shareholder communications,  listing and</t>
+        </is>
+      </c>
+      <c r="C108" t="inlineStr">
+        <is>
+          <t>Loss and comprehensive loss for the period (77,373)</t>
+        </is>
+      </c>
+      <c r="D108" t="inlineStr"/>
+      <c r="E108" s="5" t="n">
+        <v>-0.008348</v>
+      </c>
+      <c r="F108" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="G108" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="H108" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="I108" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+    </row>
+    <row r="109">
+      <c r="A109" t="inlineStr">
+        <is>
+          <t>income_statement</t>
+        </is>
+      </c>
+      <c r="B109" t="inlineStr">
+        <is>
+          <t>Transfer  agent, shareholder communications,  listing and</t>
+        </is>
+      </c>
+      <c r="C109" t="inlineStr">
+        <is>
+          <t>Basic and diluted loss per common share (Note 5) (0.02)</t>
+        </is>
+      </c>
+      <c r="D109" t="inlineStr"/>
+      <c r="E109" s="5" t="n">
+        <v>-1e-08</v>
+      </c>
+      <c r="F109" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="G109" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="H109" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="I109" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+    </row>
+    <row r="110">
+      <c r="A110" t="inlineStr">
+        <is>
+          <t>income_statement</t>
+        </is>
+      </c>
+      <c r="B110" t="inlineStr">
+        <is>
+          <t>Shares     Amount         Reserves      Deficit          Total</t>
+        </is>
+      </c>
+      <c r="C110" t="inlineStr">
+        <is>
+          <t>Balance, March 3, 2021 - - - -</t>
+        </is>
+      </c>
+      <c r="D110" t="inlineStr"/>
+      <c r="E110" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="F110" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="G110" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="H110" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="I110" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+    </row>
+    <row r="111">
+      <c r="A111" t="inlineStr">
+        <is>
+          <t>income_statement</t>
+        </is>
+      </c>
+      <c r="B111" t="inlineStr">
+        <is>
+          <t>Shares     Amount         Reserves      Deficit          Total</t>
+        </is>
+      </c>
+      <c r="C111" t="inlineStr">
+        <is>
+          <t>Shares issued 3,000,000 225,000 - -</t>
+        </is>
+      </c>
+      <c r="D111" t="inlineStr"/>
+      <c r="E111" s="5" t="n">
+        <v>0.225</v>
+      </c>
+      <c r="F111" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="G111" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="H111" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="I111" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+    </row>
+    <row r="112">
+      <c r="A112" t="inlineStr">
+        <is>
+          <t>income_statement</t>
+        </is>
+      </c>
+      <c r="B112" t="inlineStr">
+        <is>
+          <t>Shares     Amount         Reserves      Deficit          Total</t>
+        </is>
+      </c>
+      <c r="C112" t="inlineStr">
+        <is>
+          <t>Loss for the period - - - (8,348)</t>
+        </is>
+      </c>
+      <c r="D112" t="inlineStr"/>
+      <c r="E112" s="5" t="n">
+        <v>-0.008348</v>
+      </c>
+      <c r="F112" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="G112" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="H112" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="I112" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+    </row>
+    <row r="113">
+      <c r="A113" t="inlineStr">
+        <is>
+          <t>income_statement</t>
+        </is>
+      </c>
+      <c r="B113" t="inlineStr">
+        <is>
+          <t>Shares     Amount         Reserves      Deficit          Total</t>
+        </is>
+      </c>
+      <c r="C113" t="inlineStr">
+        <is>
+          <t>Balance, July 31, 2021 3,000,000 225,000 - (8,348)</t>
+        </is>
+      </c>
+      <c r="D113" t="inlineStr"/>
+      <c r="E113" s="5" t="n">
+        <v>0.216652</v>
+      </c>
+      <c r="F113" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="G113" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="H113" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="I113" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+    </row>
+    <row r="114">
+      <c r="A114" t="inlineStr">
+        <is>
+          <t>income_statement</t>
+        </is>
+      </c>
+      <c r="B114" t="inlineStr">
+        <is>
+          <t>Shares     Amount         Reserves      Deficit          Total</t>
+        </is>
+      </c>
+      <c r="C114" t="inlineStr">
+        <is>
+          <t>Shares issued 2,150,000 322,500 - -</t>
+        </is>
+      </c>
+      <c r="D114" t="inlineStr"/>
+      <c r="E114" s="5" t="n">
+        <v>0.3225</v>
+      </c>
+      <c r="F114" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="G114" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="H114" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="I114" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+    </row>
+    <row r="115">
+      <c r="A115" t="inlineStr">
+        <is>
+          <t>income_statement</t>
+        </is>
+      </c>
+      <c r="B115" t="inlineStr">
+        <is>
+          <t>Shares     Amount         Reserves      Deficit          Total</t>
+        </is>
+      </c>
+      <c r="C115" t="inlineStr">
+        <is>
+          <t>Share issuance costs - (120,421) 9,402 -</t>
+        </is>
+      </c>
+      <c r="D115" t="inlineStr"/>
+      <c r="E115" s="5" t="n">
+        <v>-0.111019</v>
+      </c>
+      <c r="F115" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="G115" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="H115" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="I115" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+    </row>
+    <row r="116">
+      <c r="A116" t="inlineStr">
+        <is>
+          <t>income_statement</t>
+        </is>
+      </c>
+      <c r="B116" t="inlineStr">
+        <is>
+          <t>Shares     Amount         Reserves      Deficit          Total</t>
+        </is>
+      </c>
+      <c r="C116" t="inlineStr">
+        <is>
+          <t>Share-based compensation - - 37,931 -</t>
+        </is>
+      </c>
+      <c r="D116" t="inlineStr"/>
+      <c r="E116" s="5" t="n">
+        <v>0.037931</v>
+      </c>
+      <c r="F116" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="G116" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="H116" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="I116" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+    </row>
+    <row r="117">
+      <c r="A117" t="inlineStr">
+        <is>
+          <t>income_statement</t>
+        </is>
+      </c>
+      <c r="B117" t="inlineStr">
+        <is>
+          <t>Shares     Amount         Reserves      Deficit          Total</t>
+        </is>
+      </c>
+      <c r="C117" t="inlineStr">
+        <is>
+          <t>Loss for the year - - - (77,373)</t>
+        </is>
+      </c>
+      <c r="D117" t="inlineStr"/>
+      <c r="E117" s="5" t="n">
+        <v>-0.077373</v>
+      </c>
+      <c r="F117" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="G117" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="H117" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="I117" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+    </row>
+    <row r="118">
+      <c r="A118" t="inlineStr">
+        <is>
+          <t>income_statement</t>
+        </is>
+      </c>
+      <c r="B118" t="inlineStr">
+        <is>
+          <t>Shares     Amount         Reserves      Deficit          Total</t>
+        </is>
+      </c>
+      <c r="C118" t="inlineStr">
         <is>
           <t>Balance, July 31, 2022 5,150,000 427,079 47,333 (85,721)</t>
         </is>
       </c>
-      <c r="D90" t="inlineStr"/>
-      <c r="E90" s="5" t="n">
+      <c r="D118" t="inlineStr"/>
+      <c r="E118" s="5" t="n">
         <v>0.388691</v>
       </c>
-      <c r="F90" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="G90" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="H90" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="I90" t="inlineStr">
+      <c r="F118" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="G118" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="H118" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="I118" t="inlineStr">
         <is>
           <t>-</t>
         </is>
